--- a/data/conflicte_militare/conflicte_militare_romania.xlsx
+++ b/data/conflicte_militare/conflicte_militare_romania.xlsx
@@ -11363,10 +11363,10 @@
         </is>
       </c>
       <c r="N115" s="2" t="n">
-        <v>47.06</v>
+        <v>47.078</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>26.95</v>
+        <v>26.56</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Ojogeni (județul Gorj) — identificare disputată</t>
+          <t>Ojogeni, pe râul Prahova, la vărsarea în Ialomița — identificare disputată</t>
         </is>
       </c>
       <c r="K131" s="2" t="n">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Gorj</t>
+          <t>Ialomița</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -12883,10 +12883,10 @@
         </is>
       </c>
       <c r="N131" s="2" t="n">
-        <v>45.12</v>
+        <v>44.7</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>23.28</v>
+        <v>26.45</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
@@ -15733,10 +15733,10 @@
         </is>
       </c>
       <c r="N161" s="2" t="n">
-        <v>47.79</v>
+        <v>47.74</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>22.89</v>
+        <v>22.68</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>

--- a/data/conflicte_militare/conflicte_militare_romania.xlsx
+++ b/data/conflicte_militare/conflicte_militare_romania.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dicționar" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Conflicte'!$A$1:$U$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Conflicte'!$A$1:$U$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U164"/>
+  <dimension ref="A1:U167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Vaslui (Podul Înalt)</t>
+          <t>Bătălia de la Lipnic</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -11227,19 +11227,19 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>1475-01-10</t>
+          <t>1469-08-20</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>1475-01-10</t>
+          <t>1470-08-20</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Podul Înalt, la sud-est de Vaslui (județul Vaslui)</t>
+          <t>Lipnic (Lipinți), pe Nistru — azi raionul Ocnița, Republica Moldova</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
@@ -11259,48 +11259,48 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Basarabia de Nord (Rep. Moldova)</t>
         </is>
       </c>
       <c r="N114" s="2" t="n">
-        <v>46.63</v>
+        <v>48.3</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>27.75</v>
+        <v>27.36</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Ștefan cel Mare) vs. Imperiul Otoman (Suleiman Pașa, armata Rumeliei)</t>
+          <t>Moldova (Ștefan cel Mare) vs. Hoarda de Aur (hanul Mamac)</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>Ștefan cel Mare obține o victorie strălucită împotriva unei armate otomane net superioare numeric, conduse de Suleiman Pașa, folosind terenul mlăștinos și tactici de ambuscadă. Victoria de la Vaslui a avut un ecou european major.</t>
+          <t>Tătarii Hoardei de Aur, conduși de hanul Mamac, invadează Moldova și pradă ținuturile ajungând la Nistru; Ștefan cel Mare îi urmărește și îi prinde în dumbrava de la Lipnic, aproape de râu. Bătălia se încheie cu o victorie zdrobitoare a moldovenilor, fiul și fratele hanului fiind luați prizonieri.</t>
         </is>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
-          <t>Victorie moldoveană decisivă</t>
+          <t>Victorie decisivă moldovenească; respingerea invaziei tătare</t>
         </is>
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Parțial (graniță/zona învecinată)</t>
         </is>
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Datarea este disputată între 20 august 1469 și 1470; localitatea se află azi în Republica Moldova.</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XV d.Hr.</t>
+          <t>batalii.csv — sec. XV d.Hr. (completare)</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Războieni / Valea Albă</t>
+          <t>Bătălia de la Vaslui (Podul Înalt)</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -11322,19 +11322,19 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>1476-07-26</t>
+          <t>1475-01-10</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>1476-07-26</t>
+          <t>1475-01-10</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Războieni / Valea Albă (județul Neamț)</t>
+          <t>Podul Înalt, la sud-est de Vaslui (județul Vaslui)</t>
         </is>
       </c>
       <c r="K115" s="2" t="n">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>Neamț</t>
+          <t>Vaslui</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -11363,24 +11363,24 @@
         </is>
       </c>
       <c r="N115" s="2" t="n">
-        <v>47.078</v>
+        <v>46.63</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>26.56</v>
+        <v>27.75</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Ștefan cel Mare) vs. Imperiul Otoman (Mehmed al II-lea)</t>
+          <t>Moldova (Ștefan cel Mare) vs. Imperiul Otoman (Suleiman Pașa, armata Rumeliei)</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
         <is>
-          <t>Oastea Moldovei este înfrântă de sultanul Mehmed al II-lea, care invadase Moldova cu o armată uriașă. Cu toate acestea, otomanii nu pot cuceri țara datorită rezistenței din cetăți și a tacticii de hărțuire, retrăgându-se în cele din urmă.</t>
+          <t>Ștefan cel Mare obține o victorie strălucită împotriva unei armate otomane net superioare numeric, conduse de Suleiman Pașa, folosind terenul mlăștinos și tactici de ambuscadă. Victoria de la Vaslui a avut un ecou european major.</t>
         </is>
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>Înfrângere militară tactică, dar victorie strategică a Moldovei</t>
+          <t>Victorie moldoveană decisivă</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
@@ -11407,41 +11407,41 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Războaiele lui Radu de la Afumați (1522–1525)</t>
+          <t>Bătălia de la Războieni / Valea Albă</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Războaie / campanii</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1476-07-26</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1476-07-26</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>1522</v>
+        <v>1476</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>1525</v>
+        <v>1476</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>sec. XVI d.Hr.</t>
+          <t>sec. XV d.Hr.</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească (bătălii la Ștefănești, Gubavi, București)</t>
+          <t>Războieni / Valea Albă (județul Neamț)</t>
         </is>
       </c>
       <c r="K116" s="2" t="n">
@@ -11449,33 +11449,33 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>Argeș / Giurgiu / Ilfov</t>
+          <t>Neamț</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N116" s="2" t="n">
-        <v>44.9</v>
+        <v>47.078</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>25</v>
+        <v>26.56</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească (Radu de la Afumați) vs. Imperiul Otoman și pretendenți sprijiniți de otomani</t>
+          <t>Moldova (Ștefan cel Mare) vs. Imperiul Otoman (Mehmed al II-lea)</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>După moartea lui Neagoe Basarab, Țara Românească trece printr-o criză succesorală profundă. Radu de la Afumați poartă circa 20 de bătălii împotriva otomanilor și a pretendenților sprijiniți de aceștia, reușind temporar să împiedice transformarea țării în pașalâc turcesc.</t>
+          <t>Oastea Moldovei este înfrântă de sultanul Mehmed al II-lea, care invadase Moldova cu o armată uriașă. Cu toate acestea, otomanii nu pot cuceri țara datorită rezistenței din cetăți și a tacticii de hărțuire, retrăgându-se în cele din urmă.</t>
         </is>
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>Menținerea autonomiei, dar cu tribut și instabilitate cronică</t>
+          <t>Înfrângere militară tactică, dar victorie strategică a Moldovei</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
@@ -11485,12 +11485,12 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>Inclus ca campanie (bătăliile individuale nu sunt detaliate în sursă).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 3</t>
+          <t>batalii.csv — sec. XV d.Hr.</t>
         </is>
       </c>
     </row>
@@ -11502,90 +11502,90 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Mohács (context — în afara teritoriului României)</t>
+          <t>Bătălia de la Câmpul Pâinii</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Bătălie (context regional)</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>1526-08-29</t>
+          <t>1479-10-13</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>1526-08-29</t>
+          <t>1479-10-13</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>1526</v>
+        <v>1479</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>1526</v>
+        <v>1479</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>sec. XVI d.Hr.</t>
+          <t>sec. XV d.Hr.</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Mohács (Ungaria) — în afara teritoriului actual al României</t>
+          <t>Câmpul Pâinii, pe luncă Mureșului între Șibot (Alba) și Orăștie (Hunedoara)</t>
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alba / Hunedoara</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Transilvania</t>
         </is>
       </c>
       <c r="N117" s="2" t="n">
-        <v>45.99</v>
+        <v>45.9</v>
       </c>
       <c r="O117" s="2" t="n">
-        <v>18.7</v>
+        <v>23.3</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>Regatul Ungariei vs. Imperiul Otoman (Soliman Magnificul)</t>
+          <t>Regatul Ungariei / Transilvania (voievodul Ștefan Báthory, banul Pavel Chinezul, judele Georg Hecht) vs. Imperiul Otoman (Ali Mihaloglu, Iskender bey) și Muntenia (Basarab Țepeluș)</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
         <is>
-          <t>Bătălia s-a dat pe teritoriul Ungariei de astăzi, dar prăbușirea Regatului Ungar a dus direct la transformarea Transilvaniei în principat autonom sub suzeranitate otomană (1541), generând conflicte interne între facțiunile nobiliare pro-habsburgice și pro-otomane pe tot parcursul secolului.</t>
+          <t>O oaste otomană puternică, sprijinită de un corp muntean, pătrunde în Transilvania prin Valea Oltului și pe Valea Sebeșului, jefuind Sebeșul, Alba Iulia și Hunedoara. Voievodul Ștefan Báthory și banul Pavel Chinezul concentrează oștile la Câmpul Pâinii, pe luncă Mureșului, unde obțin o victorie răsunătoare asupra otomanilor — una dintre cele mai mari izbânzi creștine anti-otomane din Transilvania.</t>
         </is>
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>Căderea Regatului Ungariei medievale; autonomie otomană pentru Transilvania</t>
+          <t>Victorie decisivă a oștilor creștine; respingerea marii invazii otomane</t>
         </is>
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>Nu (context regional)</t>
+          <t>Da</t>
         </is>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>Inclus ca eveniment de context regional.</t>
+          <t>Locația câmpului de luptă se află între Șibot și Orăștie, pe luncă Mureșului; data este 13 octombrie 1479.</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 5</t>
+          <t>batalii.csv — sec. XV d.Hr. (completare)</t>
         </is>
       </c>
     </row>
@@ -11597,90 +11597,90 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Feldioara</t>
+          <t>Bătălia de la Codrii Cosminului</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Bătălie / intervenție militară</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>1529-06-22</t>
+          <t>1497-10-26</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>1529-06-22</t>
+          <t>1497-10-26</t>
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>1529</v>
+        <v>1497</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1529</v>
+        <v>1497</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>sec. XVI d.Hr.</t>
+          <t>sec. XV d.Hr.</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Feldioara (județul Brașov)</t>
+          <t>Codrii Cosminului, pe valea Siretului — azi regiunea Cernăuți, Ucraina</t>
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Transilvania</t>
+          <t>Bucovina (azi Ucraina)</t>
         </is>
       </c>
       <c r="N118" s="2" t="n">
-        <v>45.82</v>
+        <v>48.15</v>
       </c>
       <c r="O118" s="2" t="n">
-        <v>25.6</v>
+        <v>26.1</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Petru Rareș) și Regatul Ungariei de Est (Ioan Zápolya) vs. adepții lui Ferdinand de Habsburg</t>
+          <t>Moldova (Ștefan cel Mare) vs. Regatul Poloniei (regele Ioan I Albert)</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>Petru Rareș intervine militar în Transilvania în sprijinul regelui Ioan Zápolya și obține o victorie categorică împotriva adepților lui Ferdinand de Habsburg, consolidând influența moldovenească în regiune.</t>
+          <t>Regele polon Ioan I Albert pornește o campanie cu pretextul recuceririi Chiliei și Cetății Albe, dar asediază Suceava. Ștefan cel Mare îl lasă să se epuizeze și atacă în ambuscadă oastea poloneză aflată în retragere prin Codrii Cosminului, în pădurile care despart valea Siretului de valea Prutului. Polonezii suferă pierderi grele, iar campania se încheie printr-o victorie moldovenească răsunătoare, considerată ultima mare bătălie a lui Ștefan cel Mare.</t>
         </is>
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>Victorie categorică a lui Petru Rareș și a lui Zápolya</t>
+          <t>Victorie decisivă moldovenească; respingerea expediției poloneze</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Nu (context regional)</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Câmpul de luptă se află azi în nordul Bucovinei (regiunea Cernăuți, Ucraina), la circa 100 km nord de Suceava; localizarea este aproximativă.</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 2</t>
+          <t>batalii.csv — sec. XV d.Hr. (completare)</t>
         </is>
       </c>
     </row>
@@ -11692,29 +11692,29 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Invazia otomană din 1538 în Moldova</t>
+          <t>Războaiele lui Radu de la Afumați (1522–1525)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Invazie</t>
+          <t>Războaie / campanii</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>1538</v>
+        <v>1522</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>1538</v>
+        <v>1525</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Moldova: Suceava (județul Suceava)</t>
+          <t>Țara Românească (bătălii la Ștefănești, Gubavi, București)</t>
         </is>
       </c>
       <c r="K119" s="2" t="n">
@@ -11734,33 +11734,33 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>Suceava</t>
+          <t>Argeș / Giurgiu / Ilfov</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Țara Românească</t>
         </is>
       </c>
       <c r="N119" s="2" t="n">
-        <v>47.65</v>
+        <v>44.9</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Otoman (Soliman Magnificul) vs. Moldova (Petru Rareș)</t>
+          <t>Țara Românească (Radu de la Afumați) vs. Imperiul Otoman și pretendenți sprijiniți de otomani</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
         <is>
-          <t>Sultanul Soliman Magnificul organizează o campanie masivă împotriva Moldovei pentru a-l pedepsi pe Petru Rareș. Din cauza trădării marii boierimi, domnitorul este nevoit să fugă în Transilvania, iar Suceava este ocupată fără luptă.</t>
+          <t>După moartea lui Neagoe Basarab, Țara Românească trece printr-o criză succesorală profundă. Radu de la Afumați poartă circa 20 de bătălii împotriva otomanilor și a pretendenților sprijiniți de aceștia, reușind temporar să împiedice transformarea țării în pașalâc turcesc.</t>
         </is>
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>Ocuparea Moldovei; dețronarea lui Petru Rareș</t>
+          <t>Menținerea autonomiei, dar cu tribut și instabilitate cronică</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
@@ -11770,12 +11770,12 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Inclus ca campanie (bătăliile individuale nu sunt detaliate în sursă).</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 2</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 3</t>
         </is>
       </c>
     </row>
@@ -11787,29 +11787,29 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Iezerul Cahulului</t>
+          <t>Bătălia de la Mohács (context — în afara teritoriului României)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Bătălie (context regional)</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1574-06</t>
+          <t>1526-08-29</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>1574-06</t>
+          <t>1526-08-29</t>
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>1574</v>
+        <v>1526</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>1574</v>
+        <v>1526</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Iezerul Cahulului, pe Prut (azi în Republica Moldova)</t>
+          <t>Mohács (Ungaria) — în afara teritoriului actual al României</t>
         </is>
       </c>
       <c r="K120" s="2" t="n">
@@ -11834,43 +11834,43 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>Moldova (sud) / Basarabia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N120" s="2" t="n">
-        <v>45.91</v>
+        <v>45.99</v>
       </c>
       <c r="O120" s="2" t="n">
-        <v>28.19</v>
+        <v>18.7</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Ioan Vodă cel Viteaz) vs. Imperiul Otoman (cu sprijinul muntean)</t>
+          <t>Regatul Ungariei vs. Imperiul Otoman (Soliman Magnificul)</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>Din cauza lipsei de apă și a trădării pârcălabului Ieremia Golia, armata moldoveană este încercuită. Deși moldovenii luptă eroic, sunt înfrânți, iar Ioan Vodă este executat de otomani.</t>
+          <t>Bătălia s-a dat pe teritoriul Ungariei de astăzi, dar prăbușirea Regatului Ungar a dus direct la transformarea Transilvaniei în principat autonom sub suzeranitate otomană (1541), generând conflicte interne între facțiunile nobiliare pro-habsburgice și pro-otomane pe tot parcursul secolului.</t>
         </is>
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>Înfrângere moldoveană; execuția lui Ioan Vodă</t>
+          <t>Căderea Regatului Ungariei medievale; autonomie otomană pentru Transilvania</t>
         </is>
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>Parțial (graniță/zona învecinată)</t>
+          <t>Nu (context regional)</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>Zona se află în afara granițelor actuale ale României (Republica Moldova).</t>
+          <t>Inclus ca eveniment de context regional.</t>
         </is>
       </c>
       <c r="U120" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 4</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 5</t>
         </is>
       </c>
     </row>
@@ -11882,29 +11882,29 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Războaiele lui Ioan Vodă cel Viteaz — Bătălia de la Jiliște</t>
+          <t>Bătălia de la Feldioara</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Bătălie / intervenție militară</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>1574-04</t>
+          <t>1529-06-22</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1574-04</t>
+          <t>1529-06-22</t>
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>1574</v>
+        <v>1529</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>1574</v>
+        <v>1529</v>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
@@ -11916,41 +11916,41 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>Jiliște — sud-estul Moldovei, zona Prutului (locație disputată)</t>
+          <t>Feldioara (județul Brașov)</t>
         </is>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>Galați / Vaslui</t>
+          <t>Brașov</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Transilvania</t>
         </is>
       </c>
       <c r="N121" s="2" t="n">
-        <v>45.95</v>
+        <v>45.82</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>28</v>
+        <v>25.6</v>
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Ioan Vodă cel Viteaz) vs. armata otomano-munteană (pentru Petru Șchiopul)</t>
+          <t>Moldova (Petru Rareș) și Regatul Ungariei de Est (Ioan Zápolya) vs. adepții lui Ferdinand de Habsburg</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
         <is>
-          <t>Ioan Vodă cel Viteaz refuză să dubleze tributul cerut de Poartă și pornește o campanie fulgerătoare. În aprilie 1574 surprinde și zdrobește o armată turco-munteană venită să-l instaleze pe Petru Șchiopul pe tronul Moldovei.</t>
+          <t>Petru Rareș intervine militar în Transilvania în sprijinul regelui Ioan Zápolya și obține o victorie categorică împotriva adepților lui Ferdinand de Habsburg, consolidând influența moldovenească în regiune.</t>
         </is>
       </c>
       <c r="R121" s="2" t="inlineStr">
         <is>
-          <t>Victorie moldoveană surprinzătoare</t>
+          <t>Victorie categorică a lui Petru Rareș și a lui Zápolya</t>
         </is>
       </c>
       <c r="S121" s="2" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>Localizarea exactă a bătăliei de la Jiliște este disputată.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 4</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 2</t>
         </is>
       </c>
     </row>
@@ -11977,29 +11977,29 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Călugăreni</t>
+          <t>Invazia otomană din 1538 în Moldova</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Invazie</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>1595-08-23</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>1595-08-23</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>1595</v>
+        <v>1538</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>1595</v>
+        <v>1538</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -12011,41 +12011,41 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Călugăreni (județul Giurgiu), râul Neajlov</t>
+          <t>Moldova: Suceava (județul Suceava)</t>
         </is>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>Giurgiu</t>
+          <t>Suceava</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N122" s="2" t="n">
-        <v>44.18</v>
+        <v>47.65</v>
       </c>
       <c r="O122" s="2" t="n">
-        <v>26.04</v>
+        <v>26.25</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească (Mihai Viteazul) vs. Imperiul Otoman (Sinan Pașa)</t>
+          <t>Imperiul Otoman (Soliman Magnificul) vs. Moldova (Petru Rareș)</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>Una dintre cele mai faimoase confruntări ale epocii: armata munteană condusă de Mihai Viteazul obține o victorie tactică importantă împotriva unei armate otomane mult superioare numeric, conduse de Sinan Pașa, folosind terenul mlăștinos de la Călugăreni.</t>
+          <t>Sultanul Soliman Magnificul organizează o campanie masivă împotriva Moldovei pentru a-l pedepsi pe Petru Rareș. Din cauza trădării marii boierimi, domnitorul este nevoit să fugă în Transilvania, iar Suceava este ocupată fără luptă.</t>
         </is>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
-          <t>Victorie tactică a lui Mihai Viteazul (retragere strategică ulterioară)</t>
+          <t>Ocuparea Moldovei; dețronarea lui Petru Rareș</t>
         </is>
       </c>
       <c r="S122" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="U122" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 2</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Giurgiu (1595)</t>
+          <t>Bătălia de la Iezerul Cahulului</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -12082,19 +12082,19 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>1595-10</t>
+          <t>1574-06</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>1595-10</t>
+          <t>1574-06</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>1595</v>
+        <v>1574</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>1595</v>
+        <v>1574</v>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
@@ -12106,56 +12106,56 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Giurgiu (județul Giurgiu)</t>
+          <t>Iezerul Cahulului, pe Prut (azi în Republica Moldova)</t>
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>Giurgiu</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească</t>
+          <t>Moldova (sud) / Basarabia</t>
         </is>
       </c>
       <c r="N123" s="2" t="n">
-        <v>43.9</v>
+        <v>45.91</v>
       </c>
       <c r="O123" s="2" t="n">
-        <v>25.97</v>
+        <v>28.19</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>Forțele aliate româno-transilvănene (Mihai Viteazul, Sigismund Báthory) vs. Imperiul Otoman (Sinan Pașa)</t>
+          <t>Moldova (Ioan Vodă cel Viteaz) vs. Imperiul Otoman (cu sprijinul muntean)</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
         <is>
-          <t>Forțele aliate ale românilor și transilvănenilor, sub comanda lui Mihai Viteazul și a lui Sigismund Báthory, zdrobesc ariergarda oastei lui Sinan Pașa care se retrăgea peste Dunăre.</t>
+          <t>Din cauza lipsei de apă și a trădării pârcălabului Ieremia Golia, armata moldoveană este încercuită. Deși moldovenii luptă eroic, sunt înfrânți, iar Ioan Vodă este executat de otomani.</t>
         </is>
       </c>
       <c r="R123" s="2" t="inlineStr">
         <is>
-          <t>Victorie aliată; distrugerea ariergardei otomane</t>
+          <t>Înfrângere moldoveană; execuția lui Ioan Vodă</t>
         </is>
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Parțial (graniță/zona învecinată)</t>
         </is>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Zona se află în afara granițelor actuale ale României (Republica Moldova).</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 4</t>
         </is>
       </c>
     </row>
@@ -12167,7 +12167,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Șelimbăr</t>
+          <t>Războaiele lui Ioan Vodă cel Viteaz — Bătălia de la Jiliște</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -12177,19 +12177,19 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>1599-10-28</t>
+          <t>1574-04</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>1599-10-28</t>
+          <t>1574-04</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>1599</v>
+        <v>1574</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1599</v>
+        <v>1574</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -12201,41 +12201,41 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Șelimbăr (județul Sibiu)</t>
+          <t>Jiliște — sud-estul Moldovei, zona Prutului (locație disputată)</t>
         </is>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>Sibiu</t>
+          <t>Galați / Vaslui</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Transilvania</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N124" s="2" t="n">
-        <v>45.77</v>
+        <v>45.95</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>24.2</v>
+        <v>28</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească (Mihai Viteazul) vs. Transilvania (cardinalul Andrei Báthory)</t>
+          <t>Moldova (Ioan Vodă cel Viteaz) vs. armata otomano-munteană (pentru Petru Șchiopul)</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>Mihai Viteazul învinge armata transilvăneană condusă de cardinalul Andrei Báthory, victorie care îi deschide calea către Alba Iulia și preluarea controlului asupra Transilvaniei.</t>
+          <t>Ioan Vodă cel Viteaz refuză să dubleze tributul cerut de Poartă și pornește o campanie fulgerătoare. În aprilie 1574 surprinde și zdrobește o armată turco-munteană venită să-l instaleze pe Petru Șchiopul pe tronul Moldovei.</t>
         </is>
       </c>
       <c r="R124" s="2" t="inlineStr">
         <is>
-          <t>Victorie a lui Mihai Viteazul; intrarea în Alba Iulia</t>
+          <t>Victorie moldoveană surprinzătoare</t>
         </is>
       </c>
       <c r="S124" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Localizarea exactă a bătăliei de la Jiliște este disputată.</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 4</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Bucov</t>
+          <t>Bătălia de la Călugăreni</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -12272,23 +12272,23 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>1600-10</t>
+          <t>1595-08-23</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>1600-10</t>
+          <t>1595-08-23</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>sec. XVI/XVII d.Hr.</t>
+          <t>sec. XVI d.Hr.</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Bucov (județul Prahova), Muntenia</t>
+          <t>Călugăreni (județul Giurgiu), râul Neajlov</t>
         </is>
       </c>
       <c r="K125" s="2" t="n">
@@ -12304,7 +12304,7 @@
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>Prahova</t>
+          <t>Giurgiu</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
@@ -12313,24 +12313,24 @@
         </is>
       </c>
       <c r="N125" s="2" t="n">
-        <v>44.97</v>
+        <v>44.18</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>26.08</v>
+        <v>26.04</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>Polonia-Lituania (Jan Zamoyski), în sprijinul lui Simion Movilă vs. Țara Românească (Mihai Viteazul)</t>
+          <t>Țara Românească (Mihai Viteazul) vs. Imperiul Otoman (Sinan Pașa)</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
         <is>
-          <t>Polonezii conduși de Jan Zamoyski îl înving pe Mihai în Muntenia, impunându-l pe tron pe Simion Movilă. Bătălia marchează pierderea temporară a Țării Românești de către Mihai.</t>
+          <t>Una dintre cele mai faimoase confruntări ale epocii: armata munteană condusă de Mihai Viteazul obține o victorie tactică importantă împotriva unei armate otomane mult superioare numeric, conduse de Sinan Pașa, folosind terenul mlăștinos de la Călugăreni.</t>
         </is>
       </c>
       <c r="R125" s="2" t="inlineStr">
         <is>
-          <t>Înfrângerea lui Mihai Viteazul; instalarea lui Simion Movilă</t>
+          <t>Victorie tactică a lui Mihai Viteazul (retragere strategică ulterioară)</t>
         </is>
       </c>
       <c r="S125" s="2" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="U125" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Mirăslău</t>
+          <t>Bătălia de la Giurgiu (1595)</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -12367,23 +12367,23 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>1600-09-18</t>
+          <t>1595-10</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>1600-09-18</t>
+          <t>1595-10</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>sec. XVI/XVII d.Hr.</t>
+          <t>sec. XVI d.Hr.</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Mirăslău (județul Alba)</t>
+          <t>Giurgiu (județul Giurgiu)</t>
         </is>
       </c>
       <c r="K126" s="2" t="n">
@@ -12399,33 +12399,33 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Alba</t>
+          <t>Giurgiu</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>Transilvania</t>
+          <t>Țara Românească</t>
         </is>
       </c>
       <c r="N126" s="2" t="n">
-        <v>46.34</v>
+        <v>43.9</v>
       </c>
       <c r="O126" s="2" t="n">
-        <v>23.68</v>
+        <v>25.97</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească/Transilvania (Mihai Viteazul) vs. nobilii maghiari răsculați și trupele imperiale habsburgice (Giorgio Basta)</t>
+          <t>Forțele aliate româno-transilvănene (Mihai Viteazul, Sigismund Báthory) vs. Imperiul Otoman (Sinan Pașa)</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>Mihai Viteazul este înfrânt de o coaliție formată din nobilii maghiari răsculați și trupele imperiale habsburgice conduse de generalul Giorgio Basta, ceea ce provoacă prăbușirea primei sale domnii în Transilvania.</t>
+          <t>Forțele aliate ale românilor și transilvănenilor, sub comanda lui Mihai Viteazul și a lui Sigismund Báthory, zdrobesc ariergarda oastei lui Sinan Pașa care se retrăgea peste Dunăre.</t>
         </is>
       </c>
       <c r="R126" s="2" t="inlineStr">
         <is>
-          <t>Înfrângerea lui Mihai Viteazul; retragerea sa din Transilvania</t>
+          <t>Victorie aliată; distrugerea ariergardei otomane</t>
         </is>
       </c>
       <c r="S126" s="2" t="inlineStr">
@@ -12435,12 +12435,12 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>Sursa îl menționează și la sec. XVII d.Hr. (recapitulare).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVI d.Hr., pct. 1; sec. XVII d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Guruslău</t>
+          <t>Bătălia de la Șelimbăr</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -12462,31 +12462,31 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>1601-08-03</t>
+          <t>1599-10-28</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>1601-08-03</t>
+          <t>1599-10-28</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>sec. XVII d.Hr.</t>
+          <t>sec. XVI d.Hr.</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Guruslău (județul Sălaj)</t>
+          <t>Șelimbăr (județul Sibiu)</t>
         </is>
       </c>
       <c r="K127" s="2" t="n">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Sălaj</t>
+          <t>Sibiu</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -12503,24 +12503,24 @@
         </is>
       </c>
       <c r="N127" s="2" t="n">
-        <v>47.23</v>
+        <v>45.77</v>
       </c>
       <c r="O127" s="2" t="n">
-        <v>23.02</v>
+        <v>24.2</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>Mihai Viteazul și generalul Giorgio Basta (Imperiul Habsburgic) vs. Sigismund Báthory</t>
+          <t>Țara Românească (Mihai Viteazul) vs. Transilvania (cardinalul Andrei Báthory)</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
         <is>
-          <t>Mihai Viteazul, aliat din nou cu generalul Basta, îl învinge pe Sigismund Báthory, restabilind controlul imperial asupra Transilvaniei cu puțin timp înainte de a fi asasinat.</t>
+          <t>Mihai Viteazul învinge armata transilvăneană condusă de cardinalul Andrei Báthory, victorie care îi deschide calea către Alba Iulia și preluarea controlului asupra Transilvaniei.</t>
         </is>
       </c>
       <c r="R127" s="2" t="inlineStr">
         <is>
-          <t>Victorie imperială; scurt timp după, asasinarea lui Mihai Viteazul</t>
+          <t>Victorie a lui Mihai Viteazul; intrarea în Alba Iulia</t>
         </is>
       </c>
       <c r="S127" s="2" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="U127" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Țuțora (1620)</t>
+          <t>Bătălia de la Bucov</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -12557,65 +12557,65 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>1620-09</t>
+          <t>1600-10</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>1620-09</t>
+          <t>1600-10</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>1620</v>
+        <v>1600</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>sec. XVII d.Hr.</t>
+          <t>sec. XVI/XVII d.Hr.</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Țuțora, pe Prut, lângă Iași (județul Iași)</t>
+          <t>Bucov (județul Prahova), Muntenia</t>
         </is>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>Iași</t>
+          <t>Prahova</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Țara Românească</t>
         </is>
       </c>
       <c r="N128" s="2" t="n">
-        <v>46.98</v>
+        <v>44.97</v>
       </c>
       <c r="O128" s="2" t="n">
-        <v>27.87</v>
+        <v>26.08</v>
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>Polonia-Lituania și Moldova (suzeranitate otomană) vs. Imperiul Otoman și tătari</t>
+          <t>Polonia-Lituania (Jan Zamoyski), în sprijinul lui Simion Movilă vs. Țara Românească (Mihai Viteazul)</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>Datorită poziției geografice, Moldova devine teatru de război în confruntările dintre polonezi și turci. Armata poloneză, care susținea Moldova, este masacrată de otomani și tătari pe malul Prutului, lângă Iași.</t>
+          <t>Polonezii conduși de Jan Zamoyski îl înving pe Mihai în Muntenia, impunându-l pe tron pe Simion Movilă. Bătălia marchează pierderea temporară a Țării Românești de către Mihai.</t>
         </is>
       </c>
       <c r="R128" s="2" t="inlineStr">
         <is>
-          <t>Masacrarea armatei poloneze; victorie otomană</t>
+          <t>Înfrângerea lui Mihai Viteazul; instalarea lui Simion Movilă</t>
         </is>
       </c>
       <c r="S128" s="2" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 4</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Hotin (1621)</t>
+          <t>Bătălia de la Mirăslău</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -12652,80 +12652,80 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>1621-09</t>
+          <t>1600-09-18</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>1621-10</t>
+          <t>1600-09-18</t>
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>1621</v>
+        <v>1600</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>1621</v>
+        <v>1600</v>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>sec. XVII d.Hr.</t>
+          <t>sec. XVI/XVII d.Hr.</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Hotin (azi în Ucraina, la granița istorică a Moldovei)</t>
+          <t>Mirăslău (județul Alba)</t>
         </is>
       </c>
       <c r="K129" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alba</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Transilvania</t>
         </is>
       </c>
       <c r="N129" s="2" t="n">
-        <v>48.51</v>
+        <v>46.34</v>
       </c>
       <c r="O129" s="2" t="n">
-        <v>26.49</v>
+        <v>23.68</v>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>Polonia-Lituania și cazaci vs. Imperiul Otoman (sultanul Osman al II-lea)</t>
+          <t>Țara Românească/Transilvania (Mihai Viteazul) vs. nobilii maghiari răsculați și trupele imperiale habsburgice (Giorgio Basta)</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
         <is>
-          <t>O mare bătălie de poziție la granița Moldovei, în care polonezii și cazacii opresc avansul armatei sultanului Osman al II-lea, evitând cucerirea zonei.</t>
+          <t>Mihai Viteazul este înfrânt de o coaliție formată din nobilii maghiari răsculați și trupele imperiale habsburgice conduse de generalul Giorgio Basta, ceea ce provoacă prăbușirea primei sale domnii în Transilvania.</t>
         </is>
       </c>
       <c r="R129" s="2" t="inlineStr">
         <is>
-          <t>Încheierea războiului prin tratat; menținerea status quo-ului</t>
+          <t>Înfrângerea lui Mihai Viteazul; retragerea sa din Transilvania</t>
         </is>
       </c>
       <c r="S129" s="2" t="inlineStr">
         <is>
-          <t>Nu (context regional)</t>
+          <t>Da</t>
         </is>
       </c>
       <c r="T129" s="2" t="inlineStr">
         <is>
-          <t>Hotinul este azi în Ucraina; inclus ca eveniment de la granița istorică a Moldovei.</t>
+          <t>Sursa îl menționează și la sec. XVII d.Hr. (recapitulare).</t>
         </is>
       </c>
       <c r="U129" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 4</t>
+          <t>batalii.csv — sec. XVI d.Hr., pct. 1; sec. XVII d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Focșani (1637)</t>
+          <t>Bătălia de la Guruslău</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -12747,19 +12747,19 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1601-08-03</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1601-08-03</t>
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>1637</v>
+        <v>1601</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>1637</v>
+        <v>1601</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Focșani (județul Vrancea), frontiera moldo-munteană</t>
+          <t>Guruslău (județul Sălaj)</t>
         </is>
       </c>
       <c r="K130" s="2" t="n">
@@ -12779,33 +12779,33 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>Vrancea</t>
+          <t>Sălaj</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>Moldova / Țara Românească</t>
+          <t>Transilvania</t>
         </is>
       </c>
       <c r="N130" s="2" t="n">
-        <v>45.7</v>
+        <v>47.23</v>
       </c>
       <c r="O130" s="2" t="n">
-        <v>27.18</v>
+        <v>23.02</v>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Vasile Lupu) vs. Țara Românească (Matei Basarab)</t>
+          <t>Mihai Viteazul și generalul Giorgio Basta (Imperiul Habsburgic) vs. Sigismund Báthory</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>Rivalitatea dintre domnitorul Moldovei, Vasile Lupu, și cel al Țării Românești, Matei Basarab, duce la mai multe ciocniri militare violente. Bătălia de la Focșani este prima confruntare directă între armatele celor doi domnitori.</t>
+          <t>Mihai Viteazul, aliat din nou cu generalul Basta, îl învinge pe Sigismund Báthory, restabilind controlul imperial asupra Transilvaniei cu puțin timp înainte de a fi asasinat.</t>
         </is>
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>Prima confruntare a războiului moldo-muntean</t>
+          <t>Victorie imperială; scurt timp după, asasinarea lui Mihai Viteazul</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="U130" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 2</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Ojogeni</t>
+          <t>Bătălia de la Țuțora (1620)</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -12842,19 +12842,19 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1620-09</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1620-09</t>
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>1639</v>
+        <v>1620</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1639</v>
+        <v>1620</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Ojogeni, pe râul Prahova, la vărsarea în Ialomița — identificare disputată</t>
+          <t>Țuțora, pe Prut, lângă Iași (județul Iași)</t>
         </is>
       </c>
       <c r="K131" s="2" t="n">
@@ -12874,33 +12874,33 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Ialomița</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N131" s="2" t="n">
-        <v>44.7</v>
+        <v>46.98</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>26.45</v>
+        <v>27.87</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Vasile Lupu) vs. Țara Românească (Matei Basarab)</t>
+          <t>Polonia-Lituania și Moldova (suzeranitate otomană) vs. Imperiul Otoman și tătari</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
         <is>
-          <t>Vasile Lupu invadează Țara Românească, dar este înfrânt decisiv de Matei Basarab în bătălia de la Ojogeni, una dintre cele mai sângeroase confruntări ale rivalității celor doi domnitori.</t>
+          <t>Datorită poziției geografice, Moldova devine teatru de război în confruntările dintre polonezi și turci. Armata poloneză, care susținea Moldova, este masacrată de otomani și tătari pe malul Prutului, lângă Iași.</t>
         </is>
       </c>
       <c r="R131" s="2" t="inlineStr">
         <is>
-          <t>Înfrângere decisivă a lui Vasile Lupu</t>
+          <t>Masacrarea armatei poloneze; victorie otomană</t>
         </is>
       </c>
       <c r="S131" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>Localizarea exactă a bătăliei este disputată.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 2</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 4</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Finta</t>
+          <t>Bătălia de la Hotin (1621)</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -12937,19 +12937,19 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>1653-05-27</t>
+          <t>1621-09</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>1653-05-27</t>
+          <t>1621-10</t>
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>1653</v>
+        <v>1621</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1653</v>
+        <v>1621</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -12961,56 +12961,56 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Finta (județul Dâmbovița)</t>
+          <t>Hotin (azi în Ucraina, la granița istorică a Moldovei)</t>
         </is>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>Dâmbovița</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N132" s="2" t="n">
-        <v>44.8</v>
+        <v>48.51</v>
       </c>
       <c r="O132" s="2" t="n">
-        <v>25.78</v>
+        <v>26.49</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească (Matei Basarab) și transilvăneni vs. Moldova (Vasile Lupu) cu cazaci (Timuș Hmelnițki)</t>
+          <t>Polonia-Lituania și cazaci vs. Imperiul Otoman (sultanul Osman al II-lea)</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>Vasile Lupu, sprijinit de cazacii ginerelui său Timuș Hmelnițki, atacă din nou Muntenia. Matei Basarab obține o victorie zdrobitoare, conflictul marcând sfârșitul domniei lui Vasile Lupu.</t>
+          <t>O mare bătălie de poziție la granița Moldovei, în care polonezii și cazacii opresc avansul armatei sultanului Osman al II-lea, evitând cucerirea zonei.</t>
         </is>
       </c>
       <c r="R132" s="2" t="inlineStr">
         <is>
-          <t>Victorie zdrobitoare a lui Matei Basarab; căderea lui Vasile Lupu</t>
+          <t>Încheierea războiului prin tratat; menținerea status quo-ului</t>
         </is>
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Nu (context regional)</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Hotinul este azi în Ucraina; inclus ca eveniment de la granița istorică a Moldovei.</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 2</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 4</t>
         </is>
       </c>
     </row>
@@ -13022,29 +13022,29 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Campania otomană de pedepsire a Transilvaniei și Bătălia de la Gilău</t>
+          <t>Bătălia de la Focșani (1637)</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Campanie / bătălie</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>1662</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>1657</v>
+        <v>1637</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1662</v>
+        <v>1637</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -13056,41 +13056,41 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Transilvania: Gilău (județul Cluj), Oradea, Crișana</t>
+          <t>Focșani (județul Vrancea), frontiera moldo-munteană</t>
         </is>
       </c>
       <c r="K133" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>Cluj / Bihor</t>
+          <t>Vrancea</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>Transilvania / Crișana</t>
+          <t>Moldova / Țara Românească</t>
         </is>
       </c>
       <c r="N133" s="2" t="n">
-        <v>46.75</v>
+        <v>45.7</v>
       </c>
       <c r="O133" s="2" t="n">
-        <v>23.38</v>
+        <v>27.18</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Otoman și tătari vs. Principatul Transilvaniei (Gheorghe Rákóczi al II-lea)</t>
+          <t>Moldova (Vasile Lupu) vs. Țara Românească (Matei Basarab)</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
         <is>
-          <t>Principele Transilvaniei Gheorghe Rákóczi al II-lea declanșează o campanie militară neautorizată în Polonia, provocând mânia Porții Otomane. Transilvania este devastată de expediții de pedepsire otomane și tătare; la Gilău (1660), Rákóczi al II-lea este rănit mortal. Otomanii cuceresc cetatea Oradea și transformă Crișana în pașalâc turcesc.</t>
+          <t>Rivalitatea dintre domnitorul Moldovei, Vasile Lupu, și cel al Țării Românești, Matei Basarab, duce la mai multe ciocniri militare violente. Bătălia de la Focșani este prima confruntare directă între armatele celor doi domnitori.</t>
         </is>
       </c>
       <c r="R133" s="2" t="inlineStr">
         <is>
-          <t>Devastarea Transilvaniei; cucerirea Oradei; pașalâc otoman în Crișana</t>
+          <t>Prima confruntare a războiului moldo-muntean</t>
         </is>
       </c>
       <c r="S133" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="U133" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 3</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 2</t>
         </is>
       </c>
     </row>
@@ -13117,29 +13117,29 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Campaniile lui Jan Sobieski în Moldova</t>
+          <t>Bătălia de la Ojogeni</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Campanii / expediții</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>1680</v>
+        <v>1639</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>1690</v>
+        <v>1639</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Moldova: Suceava, Iași, Neamț (ocupare temporară)</t>
+          <t>Ojogeni, pe râul Prahova, la vărsarea în Ialomița — identificare disputată</t>
         </is>
       </c>
       <c r="K134" s="2" t="n">
@@ -13159,33 +13159,33 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>Suceava / Iași / Neamț</t>
+          <t>Ialomița</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Țara Românească</t>
         </is>
       </c>
       <c r="N134" s="2" t="n">
-        <v>47.2</v>
+        <v>44.7</v>
       </c>
       <c r="O134" s="2" t="n">
-        <v>26.4</v>
+        <v>26.45</v>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Polonia-Lituania (regele Jan Sobieski) vs. Imperiul Otoman și Moldova (suzeranitate otomană)</t>
+          <t>Moldova (Vasile Lupu) vs. Țara Românească (Matei Basarab)</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>Polonezii organizează mai multe expediții militare în Moldova, ocupând temporar Suceava, Iașiul și Neamțul, în încercarea de a scoate principatul de sub influența otomană.</t>
+          <t>Vasile Lupu invadează Țara Românească, dar este înfrânt decisiv de Matei Basarab în bătălia de la Ojogeni, una dintre cele mai sângeroase confruntări ale rivalității celor doi domnitori.</t>
         </is>
       </c>
       <c r="R134" s="2" t="inlineStr">
         <is>
-          <t>Ocupații temporare, fără schimbarea suzeranității</t>
+          <t>Înfrângere decisivă a lui Vasile Lupu</t>
         </is>
       </c>
       <c r="S134" s="2" t="inlineStr">
@@ -13195,12 +13195,12 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Localizarea exactă a bătăliei este disputată.</t>
         </is>
       </c>
       <c r="U134" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 4</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 2</t>
         </is>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Sânmartin (1685)</t>
+          <t>Bătălia de la Finta</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -13222,19 +13222,19 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1653-05-27</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1653-05-27</t>
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>1685</v>
+        <v>1653</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>1685</v>
+        <v>1653</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
@@ -13246,41 +13246,41 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Sânmartin (posibil județul Bihor, lângă Oradea — identificare disputată)</t>
+          <t>Finta (județul Dâmbovița)</t>
         </is>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>Bihor</t>
+          <t>Dâmbovița</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>Transilvania / Crișana</t>
+          <t>Țara Românească</t>
         </is>
       </c>
       <c r="N135" s="2" t="n">
-        <v>46.99</v>
+        <v>44.8</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>21.96</v>
+        <v>25.78</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Habsburgic vs. Imperiul Otoman / forțele curuților</t>
+          <t>Țara Românească (Matei Basarab) și transilvăneni vs. Moldova (Vasile Lupu) cu cazaci (Timuș Hmelnițki)</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
         <is>
-          <t>În cadrul Marelui Război Turcesc (1683–1699), după eșecul asediului otoman asupra Vienei, Sfânta Alianță condusă de Habsburgi lansează o ofensivă puternică; luptele se desfășoară intens și pe teritoriul românesc. Bătălia de la Sânmartin (1685) este o confruntare pe teritoriul Transilvaniei între forțele imperiale și cele otomane/curuți.</t>
+          <t>Vasile Lupu, sprijinit de cazacii ginerelui său Timuș Hmelnițki, atacă din nou Muntenia. Matei Basarab obține o victorie zdrobitoare, conflictul marcând sfârșitul domniei lui Vasile Lupu.</t>
         </is>
       </c>
       <c r="R135" s="2" t="inlineStr">
         <is>
-          <t>Avans habsburgic în Transilvania</t>
+          <t>Victorie zdrobitoare a lui Matei Basarab; căderea lui Vasile Lupu</t>
         </is>
       </c>
       <c r="S135" s="2" t="inlineStr">
@@ -13290,12 +13290,12 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>Localizarea exactă a bătăliei este disputată.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U135" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 5</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 2</t>
         </is>
       </c>
     </row>
@@ -13307,29 +13307,29 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Zărnești (1690)</t>
+          <t>Campania otomană de pedepsire a Transilvaniei și Bătălia de la Gilău</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Campanie / bătălie</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>1690-08-21</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1690-08-21</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>1690</v>
+        <v>1657</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>1690</v>
+        <v>1662</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -13341,41 +13341,41 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Zărnești (județul Brașov)</t>
+          <t>Transilvania: Gilău (județul Cluj), Oradea, Crișana</t>
         </is>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>Brașov</t>
+          <t>Cluj / Bihor</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>Transilvania</t>
+          <t>Transilvania / Crișana</t>
         </is>
       </c>
       <c r="N136" s="2" t="n">
-        <v>45.58</v>
+        <v>46.75</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>25.34</v>
+        <v>23.38</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Otoman și curuți (Imre Thököly) vs. Imperiul Habsburgic</t>
+          <t>Imperiul Otoman și tătari vs. Principatul Transilvaniei (Gheorghe Rákóczi al II-lea)</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>Bătălie majoră a Marelui Război Turcesc, purtată pe teritoriul Transilvaniei: forțele otomane și curuții (conduși de Imre Thököly) înving armata imperială habsburgică, dar controlul asupra Transilvaniei se schimbă definitiv prin tratatul de la Karlowitz (1699), care cedează oficial principatul Habsburgilor.</t>
+          <t>Principele Transilvaniei Gheorghe Rákóczi al II-lea declanșează o campanie militară neautorizată în Polonia, provocând mânia Porții Otomane. Transilvania este devastată de expediții de pedepsire otomane și tătare; la Gilău (1660), Rákóczi al II-lea este rănit mortal. Otomanii cuceresc cetatea Oradea și transformă Crișana în pașalâc turcesc.</t>
         </is>
       </c>
       <c r="R136" s="2" t="inlineStr">
         <is>
-          <t>Victorie otomană/curuți; totuși, Karlowitz (1699) aduce Transilvania sub Habsburgi</t>
+          <t>Devastarea Transilvaniei; cucerirea Oradei; pașalâc otoman în Crișana</t>
         </is>
       </c>
       <c r="S136" s="2" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="U136" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVII d.Hr., pct. 5</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 3</t>
         </is>
       </c>
     </row>
@@ -13402,41 +13402,41 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Războiul Ruso-Turc (1710–1711) și Bătălia de la Stănilești</t>
+          <t>Campaniile lui Jan Sobieski în Moldova</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Război / bătălie</t>
+          <t>Campanii / expediții</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>1710</v>
+        <v>1680</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>1711</v>
+        <v>1690</v>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>sec. XVIII d.Hr.</t>
+          <t>sec. XVII d.Hr.</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Stănilești, pe Prut (județul Vaslui)</t>
+          <t>Moldova: Suceava, Iași, Neamț (ocupare temporară)</t>
         </is>
       </c>
       <c r="K137" s="2" t="n">
@@ -13444,7 +13444,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>Vaslui</t>
+          <t>Suceava / Iași / Neamț</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -13453,24 +13453,24 @@
         </is>
       </c>
       <c r="N137" s="2" t="n">
-        <v>46.63</v>
+        <v>47.2</v>
       </c>
       <c r="O137" s="2" t="n">
-        <v>28.14</v>
+        <v>26.4</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>Rusia (Petru cel Mare) și Moldova (Dimitrie Cantemir) vs. Imperiul Otoman și tătari</t>
+          <t>Polonia-Lituania (regele Jan Sobieski) vs. Imperiul Otoman și Moldova (suzeranitate otomană)</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
         <is>
-          <t>Domnitorul Moldovei, Dimitrie Cantemir, se aliază secret cu țarul Petru cel Mare (Tratatul de la Luțk), încercând să elibereze țara de suzeranitatea otomană. La Stănilești, pe Prut (iulie 1711), armatele moldo-ruse sunt încercuite și înfrânte de otomani. Cantemir se exilează în Rusia, iar Poarta introduce regimul fanariot în Moldova (1711) și apoi în Țara Românească (1716).</t>
+          <t>Polonezii organizează mai multe expediții militare în Moldova, ocupând temporar Suceava, Iașiul și Neamțul, în încercarea de a scoate principatul de sub influența otomană.</t>
         </is>
       </c>
       <c r="R137" s="2" t="inlineStr">
         <is>
-          <t>Înfrângerea moldo-rusă; introducerea regimului fanariot</t>
+          <t>Ocupații temporare, fără schimbarea suzeranității</t>
         </is>
       </c>
       <c r="S137" s="2" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="U137" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVIII d.Hr., pct. 1</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 4</t>
         </is>
       </c>
     </row>
@@ -13497,41 +13497,41 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Războiul Austro-Turc (1716–1718)</t>
+          <t>Bătălia de la Sânmartin (1685)</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Război</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>1716</v>
+        <v>1685</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1718</v>
+        <v>1685</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>sec. XVIII d.Hr.</t>
+          <t>sec. XVII d.Hr.</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Banat și Țara Românească</t>
+          <t>Sânmartin (posibil județul Bihor, lângă Oradea — identificare disputată)</t>
         </is>
       </c>
       <c r="K138" s="2" t="n">
@@ -13539,33 +13539,33 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bihor</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>Banat / Țara Românească</t>
+          <t>Transilvania / Crișana</t>
         </is>
       </c>
       <c r="N138" s="2" t="n">
-        <v>45.5</v>
+        <v>46.99</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>22</v>
+        <v>21.96</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Habsburgic vs. Imperiul Otoman</t>
+          <t>Imperiul Habsburgic vs. Imperiul Otoman / forțele curuților</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>Trupele habsburgice atacă fortărețele otomane și pătrund adânc în Banat și Țara Românească. Conflictul se încheie prin Pacea de la Passarowitz (1718), prin care Imperiul Habsburgic anexează Banatul și Oltenia (aceasta fiind retrocedată Țării Românești două decenii mai târziu).</t>
+          <t>În cadrul Marelui Război Turcesc (1683–1699), după eșecul asediului otoman asupra Vienei, Sfânta Alianță condusă de Habsburgi lansează o ofensivă puternică; luptele se desfășoară intens și pe teritoriul românesc. Bătălia de la Sânmartin (1685) este o confruntare pe teritoriul Transilvaniei între forțele imperiale și cele otomane/curuți.</t>
         </is>
       </c>
       <c r="R138" s="2" t="inlineStr">
         <is>
-          <t>Anexarea Banatului și Olteniei de către Habsburgi</t>
+          <t>Avans habsburgic în Transilvania</t>
         </is>
       </c>
       <c r="S138" s="2" t="inlineStr">
@@ -13575,12 +13575,12 @@
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Localizarea exactă a bătăliei este disputată.</t>
         </is>
       </c>
       <c r="U138" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVIII d.Hr., pct. 2</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 5</t>
         </is>
       </c>
     </row>
@@ -13592,90 +13592,90 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Războiul Ruso-Austro-Turc (1735–1739)</t>
+          <t>Bătălia de la Zărnești (1690)</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Război</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1690-08-21</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1690-08-21</t>
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>1735</v>
+        <v>1690</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>1739</v>
+        <v>1690</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>sec. XVIII d.Hr.</t>
+          <t>sec. XVII d.Hr.</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Moldova (Iași), Oltenia și Muntenia</t>
+          <t>Zărnești (județul Brașov)</t>
         </is>
       </c>
       <c r="K139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
+          <t>Brașov</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Transilvania</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="O139" s="2" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>Imperiul Otoman și curuți (Imre Thököly) vs. Imperiul Habsburgic</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>Bătălie majoră a Marelui Război Turcesc, purtată pe teritoriul Transilvaniei: forțele otomane și curuții (conduși de Imre Thököly) înving armata imperială habsburgică, dar controlul asupra Transilvaniei se schimbă definitiv prin tratatul de la Karlowitz (1699), care cedează oficial principatul Habsburgilor.</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>Victorie otomană/curuți; totuși, Karlowitz (1699) aduce Transilvania sub Habsburgi</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M139" s="2" t="inlineStr">
-        <is>
-          <t>Moldova / Oltenia / Muntenia</t>
-        </is>
-      </c>
-      <c r="N139" s="2" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="O139" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="P139" s="2" t="inlineStr">
-        <is>
-          <t>Rusia și Imperiul Habsburgic vs. Imperiul Otoman</t>
-        </is>
-      </c>
-      <c r="Q139" s="2" t="inlineStr">
-        <is>
-          <t>Teritoriul Moldovei și al Țării Românești este din nou teatru de război: trupele rusești ocupă Iașiul, iar austriecii luptă pe teritoriul Olteniei și în Muntenia. Se încheie prin Pacea de la Belgrad (1739), prin care Austria pierde Oltenia, care revine sub stăpânirea domniei de la București (și indirect sub suzeranitate otomană).</t>
-        </is>
-      </c>
-      <c r="R139" s="2" t="inlineStr">
-        <is>
-          <t>Revenirea Olteniei sub autoritatea Bucureștiului</t>
-        </is>
-      </c>
-      <c r="S139" s="2" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="T139" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="U139" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVIII d.Hr., pct. 3</t>
+          <t>batalii.csv — sec. XVII d.Hr., pct. 5</t>
         </is>
       </c>
     </row>
@@ -13687,29 +13687,29 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Războiul Ruso-Turc (1768–1774) și ocupația Principatelor</t>
+          <t>Războiul Ruso-Turc (1710–1711) și Bătălia de la Stănilești</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Război / ocupație</t>
+          <t>Război / bătălie</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>1768</v>
+        <v>1710</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>1774</v>
+        <v>1711</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Moldova și Țara Românească (Bătăliile de la Larga și Cahul — azi Republica Moldova)</t>
+          <t>Stănilești, pe Prut (județul Vaslui)</t>
         </is>
       </c>
       <c r="K140" s="2" t="n">
@@ -13729,48 +13729,48 @@
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
+          <t>Vaslui</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="O140" s="2" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>Rusia (Petru cel Mare) și Moldova (Dimitrie Cantemir) vs. Imperiul Otoman și tătari</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>Domnitorul Moldovei, Dimitrie Cantemir, se aliază secret cu țarul Petru cel Mare (Tratatul de la Luțk), încercând să elibereze țara de suzeranitatea otomană. La Stănilești, pe Prut (iulie 1711), armatele moldo-ruse sunt încercuite și înfrânte de otomani. Cantemir se exilează în Rusia, iar Poarta introduce regimul fanariot în Moldova (1711) și apoi în Țara Românească (1716).</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>Înfrângerea moldo-rusă; introducerea regimului fanariot</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M140" s="2" t="inlineStr">
-        <is>
-          <t>Moldova / Țara Românească</t>
-        </is>
-      </c>
-      <c r="N140" s="2" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="O140" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="P140" s="2" t="inlineStr">
-        <is>
-          <t>Imperiul Rus vs. Imperiul Otoman</t>
-        </is>
-      </c>
-      <c r="Q140" s="2" t="inlineStr">
-        <is>
-          <t>Unul dintre cele mai distructive conflicte ale secolului pentru spațiul românesc: Moldova și Țara Românească sunt complet ocupate de armatele țariste, iar bătăliile importante de la Larga și Cahul se dau pe teritoriul basarabean de atunci. Pacea de la Kuciuk-Kainargi (1774) retrocedează formal Principatele otomanilor, dar Rusia obține dreptul de a interveni în protejarea creștinilor; în 1775 Austria anexează nordul Moldovei (Bucovina).</t>
-        </is>
-      </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>Ocupație și distrugeri; dreptul rusesc de intervenție; anexarea Bucovinei</t>
-        </is>
-      </c>
-      <c r="S140" s="2" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="T140" s="2" t="inlineStr">
-        <is>
-          <t>Bătăliile de la Larga și Cahul au avut loc în afara granițelor actuale ale României.</t>
-        </is>
-      </c>
       <c r="U140" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVIII d.Hr., pct. 4</t>
+          <t>batalii.csv — sec. XVIII d.Hr., pct. 1</t>
         </is>
       </c>
     </row>
@@ -13782,29 +13782,29 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Războiul Ruso-Austro-Turc (1787–1792) și bătăliile de la Focșani și Râmnicu Sărat</t>
+          <t>Războiul Austro-Turc (1716–1718)</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Război / bătălii</t>
+          <t>Război</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>1787</v>
+        <v>1716</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>1792</v>
+        <v>1718</v>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>București, Iași, Focșani, Râmnicu Sărat</t>
+          <t>Banat și Țara Românească</t>
         </is>
       </c>
       <c r="K141" s="2" t="n">
@@ -13824,33 +13824,33 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>Ilfov / Iași / Vrancea / Buzău</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească / Moldova</t>
+          <t>Banat / Țara Românească</t>
         </is>
       </c>
       <c r="N141" s="2" t="n">
         <v>45.5</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>Rusia și Imperiul Habsburgic vs. Imperiul Otoman</t>
+          <t>Imperiul Habsburgic vs. Imperiul Otoman</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
         <is>
-          <t>Alianța austro-rusă atacă Imperiul Otoman pe pământ românesc: Bucureștiul și Iașiul sunt ocupate militar de trupele aliate, iar generalul rus Suvorov obține victorii răsunătoare la Focșani (1789) și Râmnicu Sărat (1789). Războiul se încheie prin Pacea de la Șiștov (1791) cu Austria și Pacea de la Iași (1792) cu Rusia, când granița rusă ajunge pentru prima dată pe Nistru.</t>
+          <t>Trupele habsburgice atacă fortărețele otomane și pătrund adânc în Banat și Țara Românească. Conflictul se încheie prin Pacea de la Passarowitz (1718), prin care Imperiul Habsburgic anexează Banatul și Oltenia (aceasta fiind retrocedată Țării Românești două decenii mai târziu).</t>
         </is>
       </c>
       <c r="R141" s="2" t="inlineStr">
         <is>
-          <t>Ocupație militară; granița rusă pe Nistru; restabilirea suzeranității otomane</t>
+          <t>Anexarea Banatului și Olteniei de către Habsburgi</t>
         </is>
       </c>
       <c r="S141" s="2" t="inlineStr">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="U141" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XVIII d.Hr., pct. 5</t>
+          <t>batalii.csv — sec. XVIII d.Hr., pct. 2</t>
         </is>
       </c>
     </row>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Războiul Ruso-Turc (1806–1812) și anexarea Basarabiei</t>
+          <t>Războiul Ruso-Austro-Turc (1735–1739)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -13887,31 +13887,31 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>1806</v>
+        <v>1735</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>1812</v>
+        <v>1739</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>sec. XIX d.Hr.</t>
+          <t>sec. XVIII d.Hr.</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Moldova (dintre Prut și Nistru) și Țara Românească</t>
+          <t>Moldova (Iași), Oltenia și Muntenia</t>
         </is>
       </c>
       <c r="K142" s="2" t="n">
@@ -13924,28 +13924,28 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Moldova / Oltenia / Muntenia</t>
         </is>
       </c>
       <c r="N142" s="2" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="O142" s="2" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Rus vs. Imperiul Otoman (principatele române ca teatru de război)</t>
+          <t>Rusia și Imperiul Habsburgic vs. Imperiul Otoman</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>Spațiul românesc este teatru de operațiuni sau ocupat militar: războiul se încheie cu Pacea de la București, prin care Imperiul Rus anexează jumătatea de est a Moldovei — teritoriul dintre Prut și Nistru, numit ulterior Basarabia.</t>
+          <t>Teritoriul Moldovei și al Țării Românești este din nou teatru de război: trupele rusești ocupă Iașiul, iar austriecii luptă pe teritoriul Olteniei și în Muntenia. Se încheie prin Pacea de la Belgrad (1739), prin care Austria pierde Oltenia, care revine sub stăpânirea domniei de la București (și indirect sub suzeranitate otomană).</t>
         </is>
       </c>
       <c r="R142" s="2" t="inlineStr">
         <is>
-          <t>Anexarea Basarabiei de către Imperiul Rus</t>
+          <t>Revenirea Olteniei sub autoritatea Bucureștiului</t>
         </is>
       </c>
       <c r="S142" s="2" t="inlineStr">
@@ -13955,12 +13955,12 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>Moștenirea teritorială a evenimentului privește și Republica Moldova de azi.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U142" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XIX d.Hr.</t>
+          <t>batalii.csv — sec. XVIII d.Hr., pct. 3</t>
         </is>
       </c>
     </row>
@@ -13972,41 +13972,41 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Revoluția lui Tudor Vladimirescu (1821)</t>
+          <t>Războiul Ruso-Turc (1768–1774) și ocupația Principatelor</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Revoltă / război intern</t>
+          <t>Război / ocupație</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>1821</v>
+        <v>1768</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>1821</v>
+        <v>1774</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>sec. XIX d.Hr.</t>
+          <t>sec. XVIII d.Hr.</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească: Gorj, Oltenia, București</t>
+          <t>Moldova și Țara Românească (Bătăliile de la Larga și Cahul — azi Republica Moldova)</t>
         </is>
       </c>
       <c r="K143" s="2" t="n">
@@ -14014,33 +14014,33 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>Gorj / Dolj / Ilfov</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească</t>
+          <t>Moldova / Țara Românească</t>
         </is>
       </c>
       <c r="N143" s="2" t="n">
-        <v>44.8</v>
+        <v>46.3</v>
       </c>
       <c r="O143" s="2" t="n">
-        <v>23.5</v>
+        <v>28</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>Pandurii lui Tudor Vladimirescu și eteriștii (Alexandru Ipsilanti) vs. Imperiul Otoman</t>
+          <t>Imperiul Rus vs. Imperiul Otoman</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
         <is>
-          <t>Mișcare socială și națională puternică în Țara Românească: se dau lupte între pandurii lui Tudor Vladimirescu, eteriștii (revoluționarii greci conduși de Alexandru Ipsilanti, care acționau tot pe teritoriu românesc) și armatele otomane venite să înăbușe revolta. Tudor Vladimirescu este în cele din urmă asasinat.</t>
+          <t>Unul dintre cele mai distructive conflicte ale secolului pentru spațiul românesc: Moldova și Țara Românească sunt complet ocupate de armatele țariste, iar bătăliile importante de la Larga și Cahul se dau pe teritoriul basarabean de atunci. Pacea de la Kuciuk-Kainargi (1774) retrocedează formal Principatele otomanilor, dar Rusia obține dreptul de a interveni în protejarea creștinilor; în 1775 Austria anexează nordul Moldovei (Bucovina).</t>
         </is>
       </c>
       <c r="R143" s="2" t="inlineStr">
         <is>
-          <t>Înăbușirea revoltei; sfârșitul lui Tudor Vladimirescu</t>
+          <t>Ocupație și distrugeri; dreptul rusesc de intervenție; anexarea Bucovinei</t>
         </is>
       </c>
       <c r="S143" s="2" t="inlineStr">
@@ -14050,12 +14050,12 @@
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bătăliile de la Larga și Cahul au avut loc în afara granițelor actuale ale României.</t>
         </is>
       </c>
       <c r="U143" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XIX d.Hr.</t>
+          <t>batalii.csv — sec. XVIII d.Hr., pct. 4</t>
         </is>
       </c>
     </row>
@@ -14067,41 +14067,41 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Războiul Ruso-Turc (1828–1829) și ocuparea Principatelor</t>
+          <t>Războiul Ruso-Austro-Turc (1787–1792) și bătăliile de la Focșani și Râmnicu Sărat</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Război / ocupație</t>
+          <t>Război / bătălii</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>1828</v>
+        <v>1787</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>1829</v>
+        <v>1792</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>sec. XIX d.Hr.</t>
+          <t>sec. XVIII d.Hr.</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Principatele Române (Moldova și Țara Românească)</t>
+          <t>București, Iași, Focșani, Râmnicu Sărat</t>
         </is>
       </c>
       <c r="K144" s="2" t="n">
@@ -14109,48 +14109,48 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
+          <t>Ilfov / Iași / Vrancea / Buzău</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Țara Românească / Moldova</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="O144" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>Rusia și Imperiul Habsburgic vs. Imperiul Otoman</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>Alianța austro-rusă atacă Imperiul Otoman pe pământ românesc: Bucureștiul și Iașiul sunt ocupate militar de trupele aliate, iar generalul rus Suvorov obține victorii răsunătoare la Focșani (1789) și Râmnicu Sărat (1789). Războiul se încheie prin Pacea de la Șiștov (1791) cu Austria și Pacea de la Iași (1792) cu Rusia, când granița rusă ajunge pentru prima dată pe Nistru.</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>Ocupație militară; granița rusă pe Nistru; restabilirea suzeranității otomane</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M144" s="2" t="inlineStr">
-        <is>
-          <t>Moldova / Țara Românească</t>
-        </is>
-      </c>
-      <c r="N144" s="2" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="O144" s="2" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="P144" s="2" t="inlineStr">
-        <is>
-          <t>Imperiul Rus vs. Imperiul Otoman</t>
-        </is>
-      </c>
-      <c r="Q144" s="2" t="inlineStr">
-        <is>
-          <t>Principatele sunt ocupate de armata țaristă. Tratatul de la Adrianopol aduce modificări economice și politice majore (instituirea Regulamentelor Organice) și retrocedează Țării Românești cetățile dunărene: Brăila, Giurgiu și Turnu.</t>
-        </is>
-      </c>
-      <c r="R144" s="2" t="inlineStr">
-        <is>
-          <t>Ocupație rusească; Regulamentele Organice; recâștigarea cetăților dunărene</t>
-        </is>
-      </c>
-      <c r="S144" s="2" t="inlineStr">
-        <is>
-          <t>Da</t>
-        </is>
-      </c>
-      <c r="T144" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="U144" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XIX d.Hr.</t>
+          <t>batalii.csv — sec. XVIII d.Hr., pct. 5</t>
         </is>
       </c>
     </row>
@@ -14162,29 +14162,29 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Revoluția de la 1848–1849 din Transilvania (război civil)</t>
+          <t>Războiul Ruso-Turc (1806–1812) și anexarea Basarabiei</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Revoluție / război civil</t>
+          <t>Război</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>1848</v>
+        <v>1806</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>1849</v>
+        <v>1812</v>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Transilvania: Munții Apuseni și diverse localități transilvănene</t>
+          <t>Moldova (dintre Prut și Nistru) și Țara Românească</t>
         </is>
       </c>
       <c r="K145" s="2" t="n">
@@ -14209,28 +14209,28 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>Transilvania</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N145" s="2" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
       <c r="O145" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>Revoluționarii maghiari vs. românii transilvăneni (Avram Iancu, aliați temporar cu Casa de Habsburg)</t>
+          <t>Imperiul Rus vs. Imperiul Otoman (principatele române ca teatru de război)</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
         <is>
-          <t>Revoluția degenerază într-un război civil sângeros între revoluționarii maghiari (care doreau unirea Transilvaniei cu Ungaria) și românii transilvăneni conduși de Avram Iancu, care apărau drepturile naționale ale românilor. Confruntările armate au loc în Munții Apuseni și în diverse localități, până la intervenția trupelor țariste, care înfrâng armata maghiară.</t>
+          <t>Spațiul românesc este teatru de operațiuni sau ocupat militar: războiul se încheie cu Pacea de la București, prin care Imperiul Rus anexează jumătatea de est a Moldovei — teritoriul dintre Prut și Nistru, numit ulterior Basarabia.</t>
         </is>
       </c>
       <c r="R145" s="2" t="inlineStr">
         <is>
-          <t>Înfrângerea armatei maghiare de către intervenția țaristă; urmări pentru națiunea română</t>
+          <t>Anexarea Basarabiei de către Imperiul Rus</t>
         </is>
       </c>
       <c r="S145" s="2" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Moștenirea teritorială a evenimentului privește și Republica Moldova de azi.</t>
         </is>
       </c>
       <c r="U145" s="2" t="inlineStr">
@@ -14257,29 +14257,29 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Războiul Crimeii — ocuparea Principatelor (1853–1856)</t>
+          <t>Revoluția lui Tudor Vladimirescu (1821)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Război / ocupații</t>
+          <t>Revoltă / război intern</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>1853</v>
+        <v>1821</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>1856</v>
+        <v>1821</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Principatele Române (Moldova și Țara Românească)</t>
+          <t>Țara Românească: Gorj, Oltenia, București</t>
         </is>
       </c>
       <c r="K146" s="2" t="n">
@@ -14299,33 +14299,33 @@
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Gorj / Dolj / Ilfov</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>Moldova / Țara Românească</t>
+          <t>Țara Românească</t>
         </is>
       </c>
       <c r="N146" s="2" t="n">
-        <v>46.5</v>
+        <v>44.8</v>
       </c>
       <c r="O146" s="2" t="n">
-        <v>26.5</v>
+        <v>23.5</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>Imperiul Rus vs. Imperiul Otoman (cu ocupări austriece și otomane de siguranță)</t>
+          <t>Pandurii lui Tudor Vladimirescu și eteriștii (Alexandru Ipsilanti) vs. Imperiul Otoman</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>Conflictul începe prin ocuparea Principatelor Române de către trupele rusești, urmată apoi de o ocupație austriacă și otomană de siguranță. Deși luptele mari se mută în Crimeea, teritoriul românesc este direct afectat de ocupații și rechiziții.</t>
+          <t>Mișcare socială și națională puternică în Țara Românească: se dau lupte între pandurii lui Tudor Vladimirescu, eteriștii (revoluționarii greci conduși de Alexandru Ipsilanti, care acționau tot pe teritoriu românesc) și armatele otomane venite să înăbușe revolta. Tudor Vladimirescu este în cele din urmă asasinat.</t>
         </is>
       </c>
       <c r="R146" s="2" t="inlineStr">
         <is>
-          <t>Ocupații succesive; restrângerea influenței ruse în principate</t>
+          <t>Înăbușirea revoltei; sfârșitul lui Tudor Vladimirescu</t>
         </is>
       </c>
       <c r="S146" s="2" t="inlineStr">
@@ -14352,29 +14352,29 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Războiul de Independență (Russo-Turc 1877–1878)</t>
+          <t>Războiul Ruso-Turc (1828–1829) și ocuparea Principatelor</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Război</t>
+          <t>Război / ocupație</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>1877-04</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>1877</v>
+        <v>1828</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>1878</v>
+        <v>1829</v>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Trecerea Dunării (Zimnicea) și luptele din Bulgaria (Plevna, Grivița, Rahova, Vidin)</t>
+          <t>Principatele Române (Moldova și Țara Românească)</t>
         </is>
       </c>
       <c r="K147" s="2" t="n">
@@ -14394,43 +14394,43 @@
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>Teleorman</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>Țara Românească / Balcani</t>
+          <t>Moldova / Țara Românească</t>
         </is>
       </c>
       <c r="N147" s="2" t="n">
-        <v>43.65</v>
+        <v>46.5</v>
       </c>
       <c r="O147" s="2" t="n">
-        <v>25.37</v>
+        <v>26.5</v>
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>România (domnitorul Carol I) și Imperiul Rus vs. Imperiul Otoman</t>
+          <t>Imperiul Rus vs. Imperiul Otoman</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
         <is>
-          <t>Armata rusă traversează România pentru a ataca Imperiul Otoman; România se alătură militar Rusiei, iar trupele conduse de Carol I au un rol decisiv în asediile de la Plevna, Grivița, Rahova și Vidin. Conflictul consfințește independența de stat a României.</t>
+          <t>Principatele sunt ocupate de armata țaristă. Tratatul de la Adrianopol aduce modificări economice și politice majore (instituirea Regulamentelor Organice) și retrocedează Țării Românești cetățile dunărene: Brăila, Giurgiu și Turnu.</t>
         </is>
       </c>
       <c r="R147" s="2" t="inlineStr">
         <is>
-          <t>Independența României (1877–1878); recunoaștere internațională</t>
+          <t>Ocupație rusească; Regulamentele Organice; recâștigarea cetăților dunărene</t>
         </is>
       </c>
       <c r="S147" s="2" t="inlineStr">
         <is>
-          <t>Parțial (graniță/zona învecinată)</t>
+          <t>Da</t>
         </is>
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>Luptele principale au avut loc în afara granițelor actuale (Bulgaria); trecerea Dunării și mobilizarea s-au desfășurat pe teritoriul românesc.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -14447,41 +14447,41 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Turtucaia</t>
+          <t>Revoluția de la 1848–1849 din Transilvania (război civil)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Revoluție / război civil</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>1916-09-02</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>1916-09-06</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>1916</v>
+        <v>1848</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1916</v>
+        <v>1849</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>sec. XX d.Hr.</t>
+          <t>sec. XIX d.Hr.</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Turtucaia (azi Tutrakan, Bulgaria) — pe malul drept al Dunării, în fața Dobrogei</t>
+          <t>Transilvania: Munții Apuseni și diverse localități transilvănene</t>
         </is>
       </c>
       <c r="K148" s="2" t="n">
@@ -14494,43 +14494,43 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>Dobrogea (graniță)</t>
+          <t>Transilvania</t>
         </is>
       </c>
       <c r="N148" s="2" t="n">
-        <v>44.05</v>
+        <v>46.3</v>
       </c>
       <c r="O148" s="2" t="n">
-        <v>26.62</v>
+        <v>23</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>România (garnizoana Turtucaia) vs. Bulgaria și Imperiul German</t>
+          <t>Revoluționarii maghiari vs. românii transilvăneni (Avram Iancu, aliați temporar cu Casa de Habsburg)</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
         <is>
-          <t>Înfrângere severă a trupelor române în fața armatei bulgaro-germane, care deschide drumul inamicului spre Dobrogea. Una dintre cele mai mari catastrofe militare ale românilor în Primul Război Mondial.</t>
+          <t>Revoluția degenerază într-un război civil sângeros între revoluționarii maghiari (care doreau unirea Transilvaniei cu Ungaria) și românii transilvăneni conduși de Avram Iancu, care apărau drepturile naționale ale românilor. Confruntările armate au loc în Munții Apuseni și în diverse localități, până la intervenția trupelor țariste, care înfrâng armata maghiară.</t>
         </is>
       </c>
       <c r="R148" s="2" t="inlineStr">
         <is>
-          <t>Înfrângere românească; ocuparea Dobrogei</t>
+          <t>Înfrângerea armatei maghiare de către intervenția țaristă; urmări pentru națiunea română</t>
         </is>
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>Nu (context regional)</t>
+          <t>Da</t>
         </is>
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>Turtucaia este azi în Bulgaria, imediat la frontiera cu România.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U148" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XX d.Hr.</t>
+          <t>batalii.csv — sec. XIX d.Hr.</t>
         </is>
       </c>
     </row>
@@ -14542,41 +14542,41 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de pe Neajlov–Argeș (1916)</t>
+          <t>Războiul Crimeii — ocuparea Principatelor (1853–1856)</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Război / ocupații</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>1916-11</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>1916-12</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>1916</v>
+        <v>1853</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>1916</v>
+        <v>1856</v>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>sec. XX d.Hr.</t>
+          <t>sec. XIX d.Hr.</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Zona râurilor Neajlov și Argeș, la sud de București</t>
+          <t>Principatele Române (Moldova și Țara Românească)</t>
         </is>
       </c>
       <c r="K149" s="2" t="n">
@@ -14584,33 +14584,33 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>Giurgiu / Ilfov</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>Muntenia</t>
+          <t>Moldova / Țara Românească</t>
         </is>
       </c>
       <c r="N149" s="2" t="n">
-        <v>44.35</v>
+        <v>46.5</v>
       </c>
       <c r="O149" s="2" t="n">
-        <v>25.75</v>
+        <v>26.5</v>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>România vs. Imperiul German (von Mackensen)</t>
+          <t>Imperiul Rus vs. Imperiul Otoman (cu ocupări austriece și otomane de siguranță)</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
         <is>
-          <t>Ultima încercare majoră de a opri înaintarea Puterilor Centrale spre București; după această confruntare, capitala este ocupată.</t>
+          <t>Conflictul începe prin ocuparea Principatelor Române de către trupele rusești, urmată apoi de o ocupație austriacă și otomană de siguranță. Deși luptele mari se mută în Crimeea, teritoriul românesc este direct afectat de ocupații și rechiziții.</t>
         </is>
       </c>
       <c r="R149" s="2" t="inlineStr">
         <is>
-          <t>Înfrângere românească; ocuparea Bucureștiului</t>
+          <t>Ocupații succesive; restrângerea influenței ruse în principate</t>
         </is>
       </c>
       <c r="S149" s="2" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="U149" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XX d.Hr.</t>
+          <t>batalii.csv — sec. XIX d.Hr.</t>
         </is>
       </c>
     </row>
@@ -14637,41 +14637,41 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de pe Valea Jiului (1916)</t>
+          <t>Războiul de Independență (Russo-Turc 1877–1878)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Război</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>1916-10</t>
+          <t>1877-04</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>1916-11</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>1916</v>
+        <v>1877</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>1916</v>
+        <v>1878</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>sec. XX d.Hr.</t>
+          <t>sec. XIX d.Hr.</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>Valea Jiului (județele Gorj/Hunedoara)</t>
+          <t>Trecerea Dunării (Zimnicea) și luptele din Bulgaria (Plevna, Grivița, Rahova, Vidin)</t>
         </is>
       </c>
       <c r="K150" s="2" t="n">
@@ -14679,48 +14679,48 @@
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>Gorj / Hunedoara</t>
+          <t>Teleorman</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>Oltenia</t>
+          <t>Țara Românească / Balcani</t>
         </is>
       </c>
       <c r="N150" s="2" t="n">
-        <v>45.35</v>
+        <v>43.65</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>23.15</v>
+        <v>25.37</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>România vs. Imperiul German (armata lui Falkenhayn)</t>
+          <t>România (domnitorul Carol I) și Imperiul Rus vs. Imperiul Otoman</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
         <is>
-          <t>Confruntare violentă prin care s-a încercat, fără succes, oprirea înaintării Puterilor Centrale, venite dinspre Transilvania prin Valea Jiului, spre București.</t>
+          <t>Armata rusă traversează România pentru a ataca Imperiul Otoman; România se alătură militar Rusiei, iar trupele conduse de Carol I au un rol decisiv în asediile de la Plevna, Grivița, Rahova și Vidin. Conflictul consfințește independența de stat a României.</t>
         </is>
       </c>
       <c r="R150" s="2" t="inlineStr">
         <is>
-          <t>Succes german inițial; depășirea apărării române</t>
+          <t>Independența României (1877–1878); recunoaștere internațională</t>
         </is>
       </c>
       <c r="S150" s="2" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Parțial (graniță/zona învecinată)</t>
         </is>
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Luptele principale au avut loc în afara granițelor actuale (Bulgaria); trecerea Dunării și mobilizarea s-au desfășurat pe teritoriul românesc.</t>
         </is>
       </c>
       <c r="U150" s="2" t="inlineStr">
         <is>
-          <t>batalii.csv — sec. XX d.Hr.</t>
+          <t>batalii.csv — sec. XIX d.Hr.</t>
         </is>
       </c>
     </row>
@@ -14732,22 +14732,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Primul Război Mondial — Campania din 1916 (înfrângerea inițială)</t>
+          <t>Bătălia de la Turtucaia</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Campanie / război</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>1916-08-27</t>
+          <t>1916-09-02</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>1916-12</t>
+          <t>1916-09-06</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>Transilvania, Muntenia, Dobrogea, Moldova (capitola de război: Iași)</t>
+          <t>Turtucaia (azi Tutrakan, Bulgaria) — pe malul drept al Dunării, în fața Dobrogei</t>
         </is>
       </c>
       <c r="K151" s="2" t="n">
@@ -14779,38 +14779,38 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>România</t>
+          <t>Dobrogea (graniță)</t>
         </is>
       </c>
       <c r="N151" s="2" t="n">
-        <v>46</v>
+        <v>44.05</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>26</v>
+        <v>26.62</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>România (Antanta) vs. Puterile Centrale (Imperiul German, Austro-Ungaria, Bulgaria)</t>
+          <t>România (garnizoana Turtucaia) vs. Bulgaria și Imperiul German</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>După o ofensivă de scurtă durată în Transilvania, armata română este nevoită să se retragă din cauza atacului combinat al trupelor germane, austro-ungare și bulgare. Sudul țării, inclusiv capitala București, este ocupat de Puterile Centrale; regele, guvernul și armata se retrag în Moldova, Iașiul devenind capitală de război.</t>
+          <t>Înfrângere severă a trupelor române în fața armatei bulgaro-germane, care deschide drumul inamicului spre Dobrogea. Una dintre cele mai mari catastrofe militare ale românilor în Primul Război Mondial.</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr">
         <is>
-          <t>Ocuparea sudului României; retragerea armatei în Moldova</t>
+          <t>Înfrângere românească; ocuparea Dobrogei</t>
         </is>
       </c>
       <c r="S151" s="2" t="inlineStr">
         <is>
-          <t>Da</t>
+          <t>Nu (context regional)</t>
         </is>
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Turtucaia este azi în Bulgaria, imediat la frontiera cu România.</t>
         </is>
       </c>
       <c r="U151" s="2" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Mărășești (1917)</t>
+          <t>Bătălia de pe Neajlov–Argeș (1916)</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -14837,19 +14837,19 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>1917-08-06</t>
+          <t>1916-11</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>1917-09-03</t>
+          <t>1916-12</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -14861,27 +14861,27 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Mărășești (județul Vrancea)</t>
+          <t>Zona râurilor Neajlov și Argeș, la sud de București</t>
         </is>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>Vrancea</t>
+          <t>Giurgiu / Ilfov</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Muntenia</t>
         </is>
       </c>
       <c r="N152" s="2" t="n">
-        <v>45.88</v>
+        <v>44.35</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>27.23</v>
+        <v>25.75</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
@@ -14890,12 +14890,12 @@
       </c>
       <c r="Q152" s="2" t="inlineStr">
         <is>
-          <t>Cea mai mare bătălie de pe frontul românesc: armata română rezistă eroic atacului german, stabilizând frontul sub deviza „Pe aici nu se trece!”.</t>
+          <t>Ultima încercare majoră de a opri înaintarea Puterilor Centrale spre București; după această confruntare, capitala este ocupată.</t>
         </is>
       </c>
       <c r="R152" s="2" t="inlineStr">
         <is>
-          <t>Victorie defensivă românească; stabilizarea frontului</t>
+          <t>Înfrângere românească; ocuparea Bucureștiului</t>
         </is>
       </c>
       <c r="S152" s="2" t="inlineStr">
@@ -14922,29 +14922,29 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Mărăști (1917)</t>
+          <t>Bătălia de pe Valea Jiului (1916)</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Bătălie / ofensivă</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>1917-07-22</t>
+          <t>1916-10</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>1917-08-01</t>
+          <t>1916-11</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
@@ -14956,41 +14956,41 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Mărăști (județul Vrancea)</t>
+          <t>Valea Jiului (județele Gorj/Hunedoara)</t>
         </is>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>Vrancea</t>
+          <t>Gorj / Hunedoara</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Oltenia</t>
         </is>
       </c>
       <c r="N153" s="2" t="n">
-        <v>45.83</v>
+        <v>45.35</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>26.77</v>
+        <v>23.15</v>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>România (generalul Alexandru Averescu) vs. Imperiul German și Austro-Ungaria</t>
+          <t>România vs. Imperiul German (armata lui Falkenhayn)</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
         <is>
-          <t>Ofensivă românească reușită, sub conducerea generalului Alexandru Averescu, prin care s-a obținut eliberarea mai multor localități și întărirea moralului armatei române reorganizate.</t>
+          <t>Confruntare violentă prin care s-a încercat, fără succes, oprirea înaintării Puterilor Centrale, venite dinspre Transilvania prin Valea Jiului, spre București.</t>
         </is>
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
-          <t>Victorie românească; eliberarea unor localități</t>
+          <t>Succes german inițial; depășirea apărării române</t>
         </is>
       </c>
       <c r="S153" s="2" t="inlineStr">
@@ -15017,29 +15017,29 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Oituz (1917)</t>
+          <t>Primul Război Mondial — Campania din 1916 (înfrângerea inițială)</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Bătălie</t>
+          <t>Campanie / război</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>1917-08-08</t>
+          <t>1916-08-27</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>1917-08-20</t>
+          <t>1916-12</t>
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Valea Oituzului (județele Bacău/Covasna)</t>
+          <t>Transilvania, Muntenia, Dobrogea, Moldova (capitola de război: Iași)</t>
         </is>
       </c>
       <c r="K154" s="2" t="n">
@@ -15059,33 +15059,33 @@
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>Bacău / Covasna</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>Moldova / Transilvania</t>
+          <t>România</t>
         </is>
       </c>
       <c r="N154" s="2" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="O154" s="2" t="n">
-        <v>26.43</v>
+        <v>26</v>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>România vs. Imperiul German și Austro-Ungaria</t>
+          <t>România (Antanta) vs. Puterile Centrale (Imperiul German, Austro-Ungaria, Bulgaria)</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
         <is>
-          <t>Desfășurată în paralel cu bătălia de la Mărășești, trupele române blochează încercarea inamicului de a pătrunde în valea Trotușului, în inima Moldovei.</t>
+          <t>După o ofensivă de scurtă durată în Transilvania, armata română este nevoită să se retragă din cauza atacului combinat al trupelor germane, austro-ungare și bulgare. Sudul țării, inclusiv capitala București, este ocupat de Puterile Centrale; regele, guvernul și armata se retrag în Moldova, Iașiul devenind capitală de război.</t>
         </is>
       </c>
       <c r="R154" s="2" t="inlineStr">
         <is>
-          <t>Victorie defensivă românească</t>
+          <t>Ocuparea sudului României; retragerea armatei în Moldova</t>
         </is>
       </c>
       <c r="S154" s="2" t="inlineStr">
@@ -15112,29 +15112,29 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Al Doilea Război Mondial — Operațiunea Tidal Wave (bombardarea Ploieștiului)</t>
+          <t>Bătălia de la Mărășești (1917)</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Bombardament aerian</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>1943-08-01</t>
+          <t>1917-08-06</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>1943-08-01</t>
+          <t>1917-09-03</t>
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>1943</v>
+        <v>1917</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>1943</v>
+        <v>1917</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Ploiești (județul Prahova)</t>
+          <t>Mărășești (județul Vrancea)</t>
         </is>
       </c>
       <c r="K155" s="2" t="n">
@@ -15154,33 +15154,33 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>Prahova</t>
+          <t>Vrancea</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>Muntenia</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N155" s="2" t="n">
-        <v>44.94</v>
+        <v>45.88</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>26.02</v>
+        <v>27.23</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>SUA (USAAF) vs. România (apărarea antiaeriană) și Germania Nazistă (apărarea rafinăriilor)</t>
+          <t>România vs. Imperiul German (von Mackensen)</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
         <is>
-          <t>Atac aerian masiv al aviației americane (USAAF) asupra rafinăriilor de petrol de la Ploiești — una dintre cele mai sângeroase și costisitoare misiuni aeriene pentru americani din întreg războiul.</t>
+          <t>Cea mai mare bătălie de pe frontul românesc: armata română rezistă eroic atacului german, stabilizând frontul sub deviza „Pe aici nu se trece!”.</t>
         </is>
       </c>
       <c r="R155" s="2" t="inlineStr">
         <is>
-          <t>Distrugeri parțiale ale rafinăriilor, cu pierderi aeriene americane mari</t>
+          <t>Victorie defensivă românească; stabilizarea frontului</t>
         </is>
       </c>
       <c r="S155" s="2" t="inlineStr">
@@ -15207,29 +15207,29 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Bombardamentele aliate asupra României (1943–1944)</t>
+          <t>Bătălia de la Mărăști (1917)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Bombardamente aeriene</t>
+          <t>Bătălie / ofensivă</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1917-07-22</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1917-08-01</t>
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>1943</v>
+        <v>1917</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>1944</v>
+        <v>1917</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -15241,41 +15241,41 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>București, Ploiești, Turnu Severin, Brașov</t>
+          <t>Mărăști (județul Vrancea)</t>
         </is>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>Ilfov / Prahova / Mehedinți / Brașov</t>
+          <t>Vrancea</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>România</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N156" s="2" t="n">
-        <v>44.8</v>
+        <v>45.83</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>25.4</v>
+        <v>26.77</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>Aliații (SUA — USAAF, Regatul Unit — RAF) vs. România și Germania Nazistă</t>
+          <t>România (generalul Alexandru Averescu) vs. Imperiul German și Austro-Ungaria</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>Înainte de intrarea trupelor terestre, România este ținta unor intense atacuri aeriene americane și britanice, având ca scop distrugerea infrastructurii petroliere și feroviare. Orașe precum București (inclusiv atacul devastator din 4 aprilie 1944 asupra Gării de Nord), Ploiești, Turnu Severin și Brașov sunt bombardate sistematic.</t>
+          <t>Ofensivă românească reușită, sub conducerea generalului Alexandru Averescu, prin care s-a obținut eliberarea mai multor localități și întărirea moralului armatei române reorganizate.</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
         <is>
-          <t>Distrugeri ale infrastructurii; victime civile numeroase</t>
+          <t>Victorie românească; eliberarea unor localități</t>
         </is>
       </c>
       <c r="S156" s="2" t="inlineStr">
@@ -15302,29 +15302,29 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>A Doua Ofensivă Iași–Chișinău (20–29 august 1944)</t>
+          <t>Bătălia de la Oituz (1917)</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Ofensivă strategică</t>
+          <t>Bătălie</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>1944-08-20</t>
+          <t>1917-08-08</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>1944-08-29</t>
+          <t>1917-08-20</t>
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>1944</v>
+        <v>1917</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>1944</v>
+        <v>1917</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Moldova: Iași, Chișinău, frontul germano-român</t>
+          <t>Valea Oituzului (județele Bacău/Covasna)</t>
         </is>
       </c>
       <c r="K157" s="2" t="n">
@@ -15344,33 +15344,33 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Iași</t>
+          <t>Bacău / Covasna</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Moldova / Transilvania</t>
         </is>
       </c>
       <c r="N157" s="2" t="n">
-        <v>47.1</v>
+        <v>46.1</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>27.5</v>
+        <v>26.43</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>URSS (Armata Roșie) vs. România și Germania Nazistă</t>
+          <t>România vs. Imperiul German și Austro-Ungaria</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>Operațiune strategică sovietică masivă care duce la prăbușirea completă a frontului germano-român din Moldova: Armata Roșie sparge rapid liniile defensive de la Iași și Chișinău. Prăbușirea militară accelerează lovitura de stat de la București din 23 august 1944.</t>
+          <t>Desfășurată în paralel cu bătălia de la Mărășești, trupele române blochează încercarea inamicului de a pătrunde în valea Trotușului, în inima Moldovei.</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
         <is>
-          <t>Prăbușirea frontului; lovitura de stat din 23 august 1944</t>
+          <t>Victorie defensivă românească</t>
         </is>
       </c>
       <c r="S157" s="2" t="inlineStr">
@@ -15397,29 +15397,29 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Păuliș (1944)</t>
+          <t>Al Doilea Război Mondial — Operațiunea Tidal Wave (bombardarea Ploieștiului)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Bătălie defensivă</t>
+          <t>Bombardament aerian</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>1944-09-14</t>
+          <t>1943-08-01</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>1944-09-19</t>
+          <t>1943-08-01</t>
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Păuliș (județul Arad)</t>
+          <t>Ploiești (județul Prahova)</t>
         </is>
       </c>
       <c r="K158" s="2" t="n">
@@ -15439,33 +15439,33 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Arad</t>
+          <t>Prahova</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>Banat</t>
+          <t>Muntenia</t>
         </is>
       </c>
       <c r="N158" s="2" t="n">
-        <v>46.12</v>
+        <v>44.94</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>21.59</v>
+        <v>26.02</v>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>România (elevii Școlii de Subofițeri de Rezervă de la Radna) vs. Ungaria (armata horthystă)</t>
+          <t>SUA (USAAF) vs. România (apărarea antiaeriană) și Germania Nazistă (apărarea rafinăriilor)</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
         <is>
-          <t>Elevii școlii de subofițeri de rezervă de la Radna opresc o ofensivă puternică a trupelor ungare, într-una dintre cele mai eroice confruntări defensive ale campaniei din vestul României.</t>
+          <t>Atac aerian masiv al aviației americane (USAAF) asupra rafinăriilor de petrol de la Ploiești — una dintre cele mai sângeroase și costisitoare misiuni aeriene pentru americani din întreg războiul.</t>
         </is>
       </c>
       <c r="R158" s="2" t="inlineStr">
         <is>
-          <t>Victorie defensivă românească împotriva forțelor superioare</t>
+          <t>Distrugeri parțiale ale rafinăriilor, cu pierderi aeriene americane mari</t>
         </is>
       </c>
       <c r="S158" s="2" t="inlineStr">
@@ -15492,26 +15492,26 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Bătălia de la Turda (1944)</t>
+          <t>Bombardamentele aliate asupra României (1943–1944)</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Bătălie de blindate</t>
+          <t>Bombardamente aeriene</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>1944-09</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>1944-10</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="G159" s="2" t="n">
         <v>1944</v>
@@ -15526,41 +15526,41 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>Turda (județul Cluj)</t>
+          <t>București, Ploiești, Turnu Severin, Brașov</t>
         </is>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>Cluj</t>
+          <t>Ilfov / Prahova / Mehedinți / Brașov</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>Transilvania</t>
+          <t>România</t>
         </is>
       </c>
       <c r="N159" s="2" t="n">
-        <v>46.57</v>
+        <v>44.8</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>23.78</v>
+        <v>25.4</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>România și URSS vs. Germania Nazistă și Ungaria</t>
+          <t>Aliații (SUA — USAAF, Regatul Unit — RAF) vs. România și Germania Nazistă</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
         <is>
-          <t>Una dintre cele mai mari și mai grele bătălii de blindate de pe teritoriul actual al României: trupele ungaro-germane opun o rezistență dârză în fața forțelor româno-sovietice, în cadrul campaniei de eliberare a Transilvaniei de Nord.</t>
+          <t>Înainte de intrarea trupelor terestre, România este ținta unor intense atacuri aeriene americane și britanice, având ca scop distrugerea infrastructurii petroliere și feroviare. Orașe precum București (inclusiv atacul devastator din 4 aprilie 1944 asupra Gării de Nord), Ploiești, Turnu Severin și Brașov sunt bombardate sistematic.</t>
         </is>
       </c>
       <c r="R159" s="2" t="inlineStr">
         <is>
-          <t>Cucerirea Turdei de către forțele româno-sovietice</t>
+          <t>Distrugeri ale infrastructurii; victime civile numeroase</t>
         </is>
       </c>
       <c r="S159" s="2" t="inlineStr">
@@ -15587,22 +15587,22 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Bătălia pentru București (august–septembrie 1944)</t>
+          <t>A Doua Ofensivă Iași–Chișinău (20–29 august 1944)</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Bătălie urbană</t>
+          <t>Ofensivă strategică</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>1944-08-24</t>
+          <t>1944-08-20</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>1944-09</t>
+          <t>1944-08-29</t>
         </is>
       </c>
       <c r="F160" s="2" t="n">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>București</t>
+          <t>Moldova: Iași, Chișinău, frontul germano-român</t>
         </is>
       </c>
       <c r="K160" s="2" t="n">
@@ -15629,33 +15629,33 @@
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>Ilfov</t>
+          <t>Iași</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>Muntenia</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="N160" s="2" t="n">
-        <v>44.43</v>
+        <v>47.1</v>
       </c>
       <c r="O160" s="2" t="n">
-        <v>26.1</v>
+        <v>27.5</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>România (armata, după 23 august) vs. Germania Nazistă</t>
+          <t>URSS (Armata Roșie) vs. România și Germania Nazistă</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
         <is>
-          <t>După actul de la 23 august 1944, teritoriul României devine teatrul unor lupte intense între foștii aliați. Trupele române resping atacurile germane care încercau să ocupe Capitala și să instaureze un regim marionetă; până la sosirea sovieticilor, Bucureștiul este deja eliberat de armata română.</t>
+          <t>Operațiune strategică sovietică masivă care duce la prăbușirea completă a frontului germano-român din Moldova: Armata Roșie sparge rapid liniile defensive de la Iași și Chișinău. Prăbușirea militară accelerează lovitura de stat de la București din 23 august 1944.</t>
         </is>
       </c>
       <c r="R160" s="2" t="inlineStr">
         <is>
-          <t>Eliberarea Bucureștiului de către armata română</t>
+          <t>Prăbușirea frontului; lovitura de stat din 23 august 1944</t>
         </is>
       </c>
       <c r="S160" s="2" t="inlineStr">
@@ -15682,22 +15682,22 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Eliberarea Careiului și Satu Mare (25 octombrie 1944)</t>
+          <t>Bătălia de la Păuliș (1944)</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Ofensivă / eliberare</t>
+          <t>Bătălie defensivă</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>1944-10</t>
+          <t>1944-09-14</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>1944-10-25</t>
+          <t>1944-09-19</t>
         </is>
       </c>
       <c r="F161" s="2" t="n">
@@ -15716,41 +15716,41 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>Carei și Satu Mare</t>
+          <t>Păuliș (județul Arad)</t>
         </is>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>Satu Mare</t>
+          <t>Arad</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>Transilvania (nord-vest)</t>
+          <t>Banat</t>
         </is>
       </c>
       <c r="N161" s="2" t="n">
-        <v>47.74</v>
+        <v>46.12</v>
       </c>
       <c r="O161" s="2" t="n">
-        <v>22.68</v>
+        <v>21.59</v>
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>România și URSS vs. Germania Nazistă și Ungaria</t>
+          <t>România (elevii Școlii de Subofițeri de Rezervă de la Radna) vs. Ungaria (armata horthystă)</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
         <is>
-          <t>Armata română, acționând împreună cu Armata Roșie, eliberează în 25 octombrie 1944 orașele Carei și Satu Mare, încheind eliberarea întregului teritoriu actual al României de sub ocupația trupelor Axei.</t>
+          <t>Elevii școlii de subofițeri de rezervă de la Radna opresc o ofensivă puternică a trupelor ungare, într-una dintre cele mai eroice confruntări defensive ale campaniei din vestul României.</t>
         </is>
       </c>
       <c r="R161" s="2" t="inlineStr">
         <is>
-          <t>Eliberarea completă a teritoriului României (25 oct. 1944)</t>
+          <t>Victorie defensivă românească împotriva forțelor superioare</t>
         </is>
       </c>
       <c r="S161" s="2" t="inlineStr">
@@ -15777,22 +15777,22 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Luptele de pe linia Dunării și din Dobrogea (1944)</t>
+          <t>Bătălia de la Turda (1944)</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Lupte de retragere / blocare</t>
+          <t>Bătălie de blindate</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>1944-08</t>
+          <t>1944-09</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>1944-09</t>
+          <t>1944-10</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
@@ -15811,41 +15811,41 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Dunărea de Jos și Dobrogea</t>
+          <t>Turda (județul Cluj)</t>
         </is>
       </c>
       <c r="K162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>Constanța / Tulcea / Călărași</t>
+          <t>Cluj</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>Dobrogea</t>
+          <t>Transilvania</t>
         </is>
       </c>
       <c r="N162" s="2" t="n">
-        <v>44.4</v>
+        <v>46.57</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>28</v>
+        <v>23.78</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>România și URSS vs. Germania Nazistă</t>
+          <t>România și URSS vs. Germania Nazistă și Ungaria</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
         <is>
-          <t>Confruntări pentru blocarea retragerii trupelor germane din Balcani, desfășurate pe linia Dunării și în Dobrogea, ca parte a luptelor de după 23 august 1944.</t>
+          <t>Una dintre cele mai mari și mai grele bătălii de blindate de pe teritoriul actual al României: trupele ungaro-germane opun o rezistență dârză în fața forțelor româno-sovietice, în cadrul campaniei de eliberare a Transilvaniei de Nord.</t>
         </is>
       </c>
       <c r="R162" s="2" t="inlineStr">
         <is>
-          <t>Blocarea și capturarea unor forțe germane care se retrăgeau</t>
+          <t>Cucerirea Turdei de către forțele româno-sovietice</t>
         </is>
       </c>
       <c r="S162" s="2" t="inlineStr">
@@ -15872,22 +15872,22 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Ofensiva Uman–Botoșani (1944)</t>
+          <t>Bătălia pentru București (august–septembrie 1944)</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Ofensivă</t>
+          <t>Bătălie urbană</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>1944-03</t>
+          <t>1944-08-24</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>1944-04</t>
+          <t>1944-09</t>
         </is>
       </c>
       <c r="F163" s="2" t="n">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>Nordul Moldovei: Botoșani, Dorohoi, Suceava</t>
+          <t>București</t>
         </is>
       </c>
       <c r="K163" s="2" t="n">
@@ -15914,33 +15914,33 @@
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>Botoșani / Suceava</t>
+          <t>Ilfov</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Muntenia</t>
         </is>
       </c>
       <c r="N163" s="2" t="n">
-        <v>47.8</v>
+        <v>44.43</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>26.5</v>
+        <v>26.1</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>URSS (Armata Roșie) vs. România și Germania Nazistă</t>
+          <t>România (armata, după 23 august) vs. Germania Nazistă</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
         <is>
-          <t>Ofensiva marchează intrarea trupelor sovietice pe teritoriul României: Frontul de Est ajunge în nordul Moldovei, iar sovieticii ocupă orașe precum Botoșani, Dorohoi și Suceava, stabilind linia frontului în nordul țării.</t>
+          <t>După actul de la 23 august 1944, teritoriul României devine teatrul unor lupte intense între foștii aliați. Trupele române resping atacurile germane care încercau să ocupe Capitala și să instaureze un regim marionetă; până la sosirea sovieticilor, Bucureștiul este deja eliberat de armata română.</t>
         </is>
       </c>
       <c r="R163" s="2" t="inlineStr">
         <is>
-          <t>Ocuparea nordului Moldovei de către Armata Roșie</t>
+          <t>Eliberarea Bucureștiului de către armata română</t>
         </is>
       </c>
       <c r="S163" s="2" t="inlineStr">
@@ -15967,22 +15967,22 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Prima Ofensivă Iași–Chișinău (1944) și bătălia de la Târgu Frumos</t>
+          <t>Eliberarea Careiului și Satu Mare (25 octombrie 1944)</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Ofensivă / bătălie de blindate</t>
+          <t>Ofensivă / eliberare</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>1944-04-08</t>
+          <t>1944-10</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>1944-06-06</t>
+          <t>1944-10-25</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
@@ -16001,61 +16001,346 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
+          <t>Carei și Satu Mare</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Transilvania (nord-vest)</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="O164" s="2" t="n">
+        <v>22.68</v>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>România și URSS vs. Germania Nazistă și Ungaria</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>Armata română, acționând împreună cu Armata Roșie, eliberează în 25 octombrie 1944 orașele Carei și Satu Mare, încheind eliberarea întregului teritoriu actual al României de sub ocupația trupelor Axei.</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>Eliberarea completă a teritoriului României (25 oct. 1944)</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>batalii.csv — sec. XX d.Hr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>RM-164</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Luptele de pe linia Dunării și din Dobrogea (1944)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Lupte de retragere / blocare</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>1944-08</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>1944-09</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>sec. XX d.Hr.</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Dunărea de Jos și Dobrogea</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>Constanța / Tulcea / Călărași</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>Dobrogea</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="O165" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>România și URSS vs. Germania Nazistă</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>Confruntări pentru blocarea retragerii trupelor germane din Balcani, desfășurate pe linia Dunării și în Dobrogea, ca parte a luptelor de după 23 august 1944.</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>Blocarea și capturarea unor forțe germane care se retrăgeau</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>batalii.csv — sec. XX d.Hr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>RM-165</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Ofensiva Uman–Botoșani (1944)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Ofensivă</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>1944-03</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1944-04</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>sec. XX d.Hr.</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Nordul Moldovei: Botoșani, Dorohoi, Suceava</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>Botoșani / Suceava</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>Moldova</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="O166" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>URSS (Armata Roșie) vs. România și Germania Nazistă</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>Ofensiva marchează intrarea trupelor sovietice pe teritoriul României: Frontul de Est ajunge în nordul Moldovei, iar sovieticii ocupă orașe precum Botoșani, Dorohoi și Suceava, stabilind linia frontului în nordul țării.</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>Ocuparea nordului Moldovei de către Armata Roșie</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>Da</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>batalii.csv — sec. XX d.Hr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>RM-166</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Prima Ofensivă Iași–Chișinău (1944) și bătălia de la Târgu Frumos</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Ofensivă / bătălie de blindate</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>1944-04-08</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>1944-06-06</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>sec. XX d.Hr.</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
           <t>Moldova: Târgu Frumos, valea Siretului, Iași–Chișinău</t>
         </is>
       </c>
-      <c r="K164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L164" s="2" t="inlineStr">
+      <c r="K167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
         <is>
           <t>Iași / Neamț</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr">
+      <c r="M167" s="2" t="inlineStr">
         <is>
           <t>Moldova</t>
         </is>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N167" s="2" t="n">
         <v>47.21</v>
       </c>
-      <c r="O164" s="2" t="n">
+      <c r="O167" s="2" t="n">
         <v>26.99</v>
       </c>
-      <c r="P164" s="2" t="inlineStr">
+      <c r="P167" s="2" t="inlineStr">
         <is>
           <t>URSS (Armata Roșie) vs. România și Germania Nazistă (generalul Hasso von Manteuffel)</t>
         </is>
       </c>
-      <c r="Q164" s="2" t="inlineStr">
+      <c r="Q167" s="2" t="inlineStr">
         <is>
           <t>Serie de lupte violente de uzură între trupele germano-române și cele sovietice. Bătălia de la Târgu Frumos este o confruntare de blindate de mare amploare, unde trupele germane și cele române reușesc temporar să oprească avansul tancurilor sovietice.</t>
         </is>
       </c>
-      <c r="R164" s="2" t="inlineStr">
+      <c r="R167" s="2" t="inlineStr">
         <is>
           <t>Stoparea temporară a ofensivei sovietice</t>
         </is>
       </c>
-      <c r="S164" s="2" t="inlineStr">
+      <c r="S167" s="2" t="inlineStr">
         <is>
           <t>Da</t>
         </is>
       </c>
-      <c r="T164" s="2" t="inlineStr">
+      <c r="T167" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U164" s="2" t="inlineStr">
+      <c r="U167" s="2" t="inlineStr">
         <is>
           <t>batalii.csv — sec. XX d.Hr.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U164"/>
+  <autoFilter ref="A1:U167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16066,7 +16351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B199"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -16092,7 +16377,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
@@ -16102,7 +16387,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4">
@@ -16112,7 +16397,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -16122,7 +16407,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -16180,17 +16465,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sec. I î.Hr.</t>
+          <t>sec. XV d.Hr.</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sec. III d.Hr.</t>
+          <t>sec. I î.Hr.</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -16200,17 +16485,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sec. III î.Hr.</t>
+          <t>sec. III d.Hr.</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sec. I d.Hr.</t>
+          <t>sec. III î.Hr.</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -16220,7 +16505,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sec. IV d.Hr.</t>
+          <t>sec. I d.Hr.</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -16230,7 +16515,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sec. IX d.Hr.</t>
+          <t>sec. IV d.Hr.</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -16240,7 +16525,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sec. X d.Hr.</t>
+          <t>sec. IX d.Hr.</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -16250,7 +16535,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sec. XIX d.Hr.</t>
+          <t>sec. X d.Hr.</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -16260,17 +16545,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>sec. V î.Hr.</t>
+          <t>sec. XIX d.Hr.</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sec. XI d.Hr.</t>
+          <t>sec. V î.Hr.</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -16280,7 +16565,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sec. XII d.Hr.</t>
+          <t>sec. XI d.Hr.</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -16290,7 +16575,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sec. XIII d.Hr.</t>
+          <t>sec. XII d.Hr.</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -16300,7 +16585,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sec. XV d.Hr.</t>
+          <t>sec. XIII d.Hr.</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -16466,7 +16751,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
@@ -17498,7 +17783,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146">
@@ -17974,7 +18259,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Moldova (sud) / Basarabia</t>
+          <t>Basarabia de Nord (Rep. Moldova)</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -17984,7 +18269,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Banat / Țara Românească</t>
+          <t>Bucovina (azi Ucraina)</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -17994,7 +18279,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Moldova / Oltenia / Muntenia</t>
+          <t>Moldova (sud) / Basarabia</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -18004,7 +18289,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Țara Românească / Moldova</t>
+          <t>Banat / Țara Românească</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -18014,7 +18299,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Țara Românească / Balcani</t>
+          <t>Moldova / Oltenia / Muntenia</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -18024,7 +18309,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Moldova / Transilvania</t>
+          <t>Țara Românească / Moldova</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -18034,10 +18319,30 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>Țara Românească / Balcani</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Moldova / Transilvania</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>Transilvania (nord-vest)</t>
         </is>
       </c>
-      <c r="B199" t="n">
+      <c r="B201" t="n">
         <v>1</v>
       </c>
     </row>
